--- a/app/data/Reference/guide.xlsx
+++ b/app/data/Reference/guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csvnewzealand-my.sharepoint.com/personal/mike_csv_co_nz/Documents/06_Altitude/Altitude/app/data/Reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="8_{BCBC3A3A-E0FA-4AA3-8593-2140AD00DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ADEE18-28C3-4D29-9424-A1EA4BBE2857}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{BCBC3A3A-E0FA-4AA3-8593-2140AD00DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293F27D8-757B-47A2-88BF-67F36C935195}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" xr2:uid="{8E4D9682-10B3-4A32-8A23-CE2B94AA5C11}"/>
+    <workbookView xWindow="17160" yWindow="-21600" windowWidth="19380" windowHeight="20970" xr2:uid="{8E4D9682-10B3-4A32-8A23-CE2B94AA5C11}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4723" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5116" uniqueCount="949">
   <si>
     <t>Tick</t>
   </si>
@@ -2891,6 +2891,18 @@
   </si>
   <si>
     <t>Apartment</t>
+  </si>
+  <si>
+    <t>Style</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Fill</t>
+  </si>
+  <si>
+    <t>Bar</t>
   </si>
 </sst>
 </file>
@@ -3437,7 +3449,16 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3453,12 +3474,6 @@
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <fill>
@@ -3482,8 +3497,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}" name="Guide" displayName="Guide" ref="A1:Q394" totalsRowShown="0">
-  <autoFilter ref="A1:Q394" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}" name="Guide" displayName="Guide" ref="A1:R394" totalsRowShown="0">
+  <autoFilter ref="A1:R394" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}">
+    <filterColumn colId="15">
+      <filters>
+        <filter val="NA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O34">
     <sortCondition ref="A2:A34"/>
     <sortCondition ref="D2:D34"/>
@@ -3491,13 +3512,13 @@
     <sortCondition ref="F2:F34"/>
     <sortCondition ref="C2:C34"/>
   </sortState>
-  <tableColumns count="17">
+  <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{1E105523-1F9A-490B-B3B3-B8269576F2CA}" name="Dataset"/>
     <tableColumn id="2" xr3:uid="{3395981A-EBAB-4924-9326-47FB19E5DA48}" name="DatasetColumn"/>
     <tableColumn id="3" xr3:uid="{E3BF457C-F7A0-47B3-B2CD-5F811C035414}" name="ColumnName"/>
-    <tableColumn id="4" xr3:uid="{C7A9722C-DC29-4AF5-B9B8-05CBCA5D36F8}" name="Category_1" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{8125AED4-99A7-4E7E-9003-2D1CDDE68C99}" name="Category_2" dataDxfId="0"/>
-    <tableColumn id="17" xr3:uid="{3D3C7246-D15C-427C-8A0E-171F32F2F1EE}" name="Level_1_Order" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{C7A9722C-DC29-4AF5-B9B8-05CBCA5D36F8}" name="Category_1" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{8125AED4-99A7-4E7E-9003-2D1CDDE68C99}" name="Category_2" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{3D3C7246-D15C-427C-8A0E-171F32F2F1EE}" name="Level_1_Order" dataDxfId="3"/>
     <tableColumn id="15" xr3:uid="{C81B58F0-59F7-483F-9A57-480268B28ECE}" name="Level_1"/>
     <tableColumn id="16" xr3:uid="{C2D32ECC-FFE5-42E9-A2FA-C589A7F771B2}" name="Level_2"/>
     <tableColumn id="18" xr3:uid="{80FF5F57-A832-41D8-B591-66D040656FDD}" name="Series_1"/>
@@ -3507,10 +3528,11 @@
     <tableColumn id="8" xr3:uid="{CD0AAC95-D2CD-4D30-9011-9942EBEBB4C1}" name="Dim_Label"/>
     <tableColumn id="9" xr3:uid="{20D4E739-3650-49F4-B4E1-DAD4BEFED02E}" name="Tick"/>
     <tableColumn id="10" xr3:uid="{FF813B21-86DC-48A9-A6EA-F4F229F2A91A}" name="Prefix"/>
-    <tableColumn id="5" xr3:uid="{58341DB7-5CB8-472C-8948-416C2373B4BA}" name="Row" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{A960F109-EFC6-45B0-838E-89D0D182C4EE}" name="Style" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{58341DB7-5CB8-472C-8948-416C2373B4BA}" name="Row" dataDxfId="2">
       <calculatedColumnFormula>ROW(Guide[[#This Row],[Row]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D6E30528-2360-40F7-A607-B78AA4014508}" name="Stack" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{D6E30528-2360-40F7-A607-B78AA4014508}" name="Stack" dataDxfId="1">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</calculatedColumnFormula>
     </tableColumn>
@@ -3836,7 +3858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D99BAD0-8494-4CE9-A247-A006F24ADF8E}">
-  <dimension ref="A1:Q394"/>
+  <dimension ref="A1:R394"/>
   <sheetFormatPr defaultRowHeight="10.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
@@ -3850,7 +3872,7 @@
     <col min="13" max="13" width="12.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -3897,13 +3919,16 @@
         <v>1</v>
       </c>
       <c r="P1" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3931,17 +3956,20 @@
       <c r="N2" t="s">
         <v>5</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q2">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>2</v>
       </c>
-      <c r="Q2" cm="1">
-        <f t="array" ref="Q2">_xlfn.XLOOKUP(
+      <c r="R2" cm="1">
+        <f t="array" ref="R2">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3973,17 +4001,20 @@
       <c r="N3" t="s">
         <v>5</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q3">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>3</v>
       </c>
-      <c r="Q3" cm="1">
-        <f t="array" ref="Q3">_xlfn.XLOOKUP(
+      <c r="R3" cm="1">
+        <f t="array" ref="R3">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -4015,17 +4046,20 @@
       <c r="N4" t="s">
         <v>5</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q4">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>4</v>
       </c>
-      <c r="Q4" cm="1">
-        <f t="array" ref="Q4">_xlfn.XLOOKUP(
+      <c r="R4" cm="1">
+        <f t="array" ref="R4">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -4057,17 +4091,20 @@
       <c r="N5" t="s">
         <v>5</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q5">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>5</v>
       </c>
-      <c r="Q5" cm="1">
-        <f t="array" ref="Q5">_xlfn.XLOOKUP(
+      <c r="R5" cm="1">
+        <f t="array" ref="R5">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -4099,17 +4136,20 @@
       <c r="N6" t="s">
         <v>5</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q6">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>6</v>
       </c>
-      <c r="Q6" cm="1">
-        <f t="array" ref="Q6">_xlfn.XLOOKUP(
+      <c r="R6" cm="1">
+        <f t="array" ref="R6">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -4141,17 +4181,20 @@
       <c r="N7" t="s">
         <v>5</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q7">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>7</v>
       </c>
-      <c r="Q7" cm="1">
-        <f t="array" ref="Q7">_xlfn.XLOOKUP(
+      <c r="R7" cm="1">
+        <f t="array" ref="R7">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -4183,17 +4226,20 @@
       <c r="N8" t="s">
         <v>5</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q8">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>8</v>
       </c>
-      <c r="Q8" cm="1">
-        <f t="array" ref="Q8">_xlfn.XLOOKUP(
+      <c r="R8" cm="1">
+        <f t="array" ref="R8">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -4225,17 +4271,20 @@
       <c r="N9" t="s">
         <v>5</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q9">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>9</v>
       </c>
-      <c r="Q9" cm="1">
-        <f t="array" ref="Q9">_xlfn.XLOOKUP(
+      <c r="R9" cm="1">
+        <f t="array" ref="R9">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -4267,17 +4316,20 @@
       <c r="N10" t="s">
         <v>5</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q10">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>10</v>
       </c>
-      <c r="Q10" cm="1">
-        <f t="array" ref="Q10">_xlfn.XLOOKUP(
+      <c r="R10" cm="1">
+        <f t="array" ref="R10">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -4317,17 +4369,20 @@
       <c r="N11" t="s">
         <v>107</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q11">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>11</v>
       </c>
-      <c r="Q11" cm="1">
-        <f t="array" ref="Q11">_xlfn.XLOOKUP(
+      <c r="R11" cm="1">
+        <f t="array" ref="R11">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -4370,17 +4425,20 @@
       <c r="O12" t="s">
         <v>10</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q12">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>12</v>
       </c>
-      <c r="Q12" cm="1">
-        <f t="array" ref="Q12">_xlfn.XLOOKUP(
+      <c r="R12" cm="1">
+        <f t="array" ref="R12">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -4423,17 +4481,20 @@
       <c r="O13" t="s">
         <v>116</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q13">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>13</v>
       </c>
-      <c r="Q13" cm="1">
-        <f t="array" ref="Q13">_xlfn.XLOOKUP(
+      <c r="R13" cm="1">
+        <f t="array" ref="R13">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -4476,17 +4537,20 @@
       <c r="O14" t="s">
         <v>10</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q14">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>14</v>
       </c>
-      <c r="Q14" cm="1">
-        <f t="array" ref="Q14">_xlfn.XLOOKUP(
+      <c r="R14" cm="1">
+        <f t="array" ref="R14">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>102</v>
       </c>
@@ -4529,17 +4593,20 @@
       <c r="O15" t="s">
         <v>124</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q15">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>15</v>
       </c>
-      <c r="Q15" cm="1">
-        <f t="array" ref="Q15">_xlfn.XLOOKUP(
+      <c r="R15" cm="1">
+        <f t="array" ref="R15">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -4582,17 +4649,20 @@
       <c r="O16" t="s">
         <v>129</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q16">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>16</v>
       </c>
-      <c r="Q16" cm="1">
-        <f t="array" ref="Q16">_xlfn.XLOOKUP(
+      <c r="R16" cm="1">
+        <f t="array" ref="R16">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -4635,17 +4705,20 @@
       <c r="O17" t="s">
         <v>10</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q17">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>17</v>
       </c>
-      <c r="Q17" cm="1">
-        <f t="array" ref="Q17">_xlfn.XLOOKUP(
+      <c r="R17" cm="1">
+        <f t="array" ref="R17">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
@@ -4688,17 +4761,20 @@
       <c r="O18" t="s">
         <v>138</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q18">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>18</v>
       </c>
-      <c r="Q18" cm="1">
-        <f t="array" ref="Q18">_xlfn.XLOOKUP(
+      <c r="R18" cm="1">
+        <f t="array" ref="R18">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -4741,17 +4817,20 @@
       <c r="O19" t="s">
         <v>124</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q19">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>19</v>
       </c>
-      <c r="Q19" cm="1">
-        <f t="array" ref="Q19">_xlfn.XLOOKUP(
+      <c r="R19" cm="1">
+        <f t="array" ref="R19">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -4794,17 +4873,20 @@
       <c r="O20" t="s">
         <v>147</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q20">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>20</v>
       </c>
-      <c r="Q20" cm="1">
-        <f t="array" ref="Q20">_xlfn.XLOOKUP(
+      <c r="R20" cm="1">
+        <f t="array" ref="R20">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -4847,17 +4929,20 @@
       <c r="O21" t="s">
         <v>10</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q21">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>21</v>
       </c>
-      <c r="Q21" cm="1">
-        <f t="array" ref="Q21">_xlfn.XLOOKUP(
+      <c r="R21" cm="1">
+        <f t="array" ref="R21">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4900,17 +4985,20 @@
       <c r="O22" t="s">
         <v>156</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q22">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>22</v>
       </c>
-      <c r="Q22" cm="1">
-        <f t="array" ref="Q22">_xlfn.XLOOKUP(
+      <c r="R22" cm="1">
+        <f t="array" ref="R22">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>102</v>
       </c>
@@ -4953,17 +5041,20 @@
       <c r="O23" t="s">
         <v>161</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q23">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>23</v>
       </c>
-      <c r="Q23" cm="1">
-        <f t="array" ref="Q23">_xlfn.XLOOKUP(
+      <c r="R23" cm="1">
+        <f t="array" ref="R23">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>102</v>
       </c>
@@ -5006,17 +5097,20 @@
       <c r="O24" t="s">
         <v>10</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q24">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>24</v>
       </c>
-      <c r="Q24" cm="1">
-        <f t="array" ref="Q24">_xlfn.XLOOKUP(
+      <c r="R24" cm="1">
+        <f t="array" ref="R24">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -5059,17 +5153,20 @@
       <c r="O25" t="s">
         <v>10</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q25">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>25</v>
       </c>
-      <c r="Q25" cm="1">
-        <f t="array" ref="Q25">_xlfn.XLOOKUP(
+      <c r="R25" cm="1">
+        <f t="array" ref="R25">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -5112,17 +5209,20 @@
       <c r="O26" t="s">
         <v>174</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q26">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>26</v>
       </c>
-      <c r="Q26" cm="1">
-        <f t="array" ref="Q26">_xlfn.XLOOKUP(
+      <c r="R26" cm="1">
+        <f t="array" ref="R26">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -5165,17 +5265,20 @@
       <c r="O27" t="s">
         <v>179</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q27">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>27</v>
       </c>
-      <c r="Q27" cm="1">
-        <f t="array" ref="Q27">_xlfn.XLOOKUP(
+      <c r="R27" cm="1">
+        <f t="array" ref="R27">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>102</v>
       </c>
@@ -5218,17 +5321,20 @@
       <c r="O28" t="s">
         <v>184</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q28">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>28</v>
       </c>
-      <c r="Q28" cm="1">
-        <f t="array" ref="Q28">_xlfn.XLOOKUP(
+      <c r="R28" cm="1">
+        <f t="array" ref="R28">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>102</v>
       </c>
@@ -5268,17 +5374,20 @@
       <c r="N29" t="s">
         <v>107</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q29">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>29</v>
       </c>
-      <c r="Q29" cm="1">
-        <f t="array" ref="Q29">_xlfn.XLOOKUP(
+      <c r="R29" cm="1">
+        <f t="array" ref="R29">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>190</v>
       </c>
@@ -5318,17 +5427,20 @@
       <c r="N30" t="s">
         <v>194</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q30">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>30</v>
       </c>
-      <c r="Q30" cm="1">
-        <f t="array" ref="Q30">_xlfn.XLOOKUP(
+      <c r="R30" cm="1">
+        <f t="array" ref="R30">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>190</v>
       </c>
@@ -5368,17 +5480,20 @@
       <c r="N31" t="s">
         <v>194</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q31">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>31</v>
       </c>
-      <c r="Q31" cm="1">
-        <f t="array" ref="Q31">_xlfn.XLOOKUP(
+      <c r="R31" cm="1">
+        <f t="array" ref="R31">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>190</v>
       </c>
@@ -5418,17 +5533,20 @@
       <c r="N32" t="s">
         <v>194</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q32">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>32</v>
       </c>
-      <c r="Q32" cm="1">
-        <f t="array" ref="Q32">_xlfn.XLOOKUP(
+      <c r="R32" cm="1">
+        <f t="array" ref="R32">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>190</v>
       </c>
@@ -5468,17 +5586,20 @@
       <c r="N33" t="s">
         <v>194</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q33">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>33</v>
       </c>
-      <c r="Q33" cm="1">
-        <f t="array" ref="Q33">_xlfn.XLOOKUP(
+      <c r="R33" cm="1">
+        <f t="array" ref="R33">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>190</v>
       </c>
@@ -5518,17 +5639,20 @@
       <c r="N34" t="s">
         <v>194</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q34">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>34</v>
       </c>
-      <c r="Q34" cm="1">
-        <f t="array" ref="Q34">_xlfn.XLOOKUP(
+      <c r="R34" cm="1">
+        <f t="array" ref="R34">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>190</v>
       </c>
@@ -5568,17 +5692,20 @@
       <c r="N35" t="s">
         <v>194</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q35">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>35</v>
       </c>
-      <c r="Q35" cm="1">
-        <f t="array" ref="Q35">_xlfn.XLOOKUP(
+      <c r="R35" cm="1">
+        <f t="array" ref="R35">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>190</v>
       </c>
@@ -5618,17 +5745,20 @@
       <c r="N36" t="s">
         <v>194</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q36">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>36</v>
       </c>
-      <c r="Q36" cm="1">
-        <f t="array" ref="Q36">_xlfn.XLOOKUP(
+      <c r="R36" cm="1">
+        <f t="array" ref="R36">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>190</v>
       </c>
@@ -5668,17 +5798,20 @@
       <c r="N37" t="s">
         <v>194</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q37">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>37</v>
       </c>
-      <c r="Q37" cm="1">
-        <f t="array" ref="Q37">_xlfn.XLOOKUP(
+      <c r="R37" cm="1">
+        <f t="array" ref="R37">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>190</v>
       </c>
@@ -5718,17 +5851,20 @@
       <c r="N38" t="s">
         <v>194</v>
       </c>
-      <c r="P38">
+      <c r="P38" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q38">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>38</v>
       </c>
-      <c r="Q38" cm="1">
-        <f t="array" ref="Q38">_xlfn.XLOOKUP(
+      <c r="R38" cm="1">
+        <f t="array" ref="R38">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>190</v>
       </c>
@@ -5768,17 +5904,20 @@
       <c r="N39" t="s">
         <v>194</v>
       </c>
-      <c r="P39">
+      <c r="P39" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q39">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>39</v>
       </c>
-      <c r="Q39" cm="1">
-        <f t="array" ref="Q39">_xlfn.XLOOKUP(
+      <c r="R39" cm="1">
+        <f t="array" ref="R39">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>220</v>
       </c>
@@ -5818,17 +5957,20 @@
       <c r="N40" t="s">
         <v>5</v>
       </c>
-      <c r="P40">
+      <c r="P40" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q40">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>40</v>
       </c>
-      <c r="Q40" cm="1">
-        <f t="array" ref="Q40">_xlfn.XLOOKUP(
+      <c r="R40" cm="1">
+        <f t="array" ref="R40">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>220</v>
       </c>
@@ -5868,17 +6010,20 @@
       <c r="N41" t="s">
         <v>5</v>
       </c>
-      <c r="P41">
+      <c r="P41" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q41">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>41</v>
       </c>
-      <c r="Q41" cm="1">
-        <f t="array" ref="Q41">_xlfn.XLOOKUP(
+      <c r="R41" cm="1">
+        <f t="array" ref="R41">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>220</v>
       </c>
@@ -5918,17 +6063,20 @@
       <c r="N42" t="s">
         <v>5</v>
       </c>
-      <c r="P42">
+      <c r="P42" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q42">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>42</v>
       </c>
-      <c r="Q42" cm="1">
-        <f t="array" ref="Q42">_xlfn.XLOOKUP(
+      <c r="R42" cm="1">
+        <f t="array" ref="R42">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>220</v>
       </c>
@@ -5968,17 +6116,20 @@
       <c r="N43" t="s">
         <v>5</v>
       </c>
-      <c r="P43">
+      <c r="P43" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q43">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>43</v>
       </c>
-      <c r="Q43" cm="1">
-        <f t="array" ref="Q43">_xlfn.XLOOKUP(
+      <c r="R43" cm="1">
+        <f t="array" ref="R43">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>220</v>
       </c>
@@ -6018,17 +6169,20 @@
       <c r="N44" t="s">
         <v>5</v>
       </c>
-      <c r="P44">
+      <c r="P44" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q44">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>44</v>
       </c>
-      <c r="Q44" cm="1">
-        <f t="array" ref="Q44">_xlfn.XLOOKUP(
+      <c r="R44" cm="1">
+        <f t="array" ref="R44">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>220</v>
       </c>
@@ -6068,17 +6222,20 @@
       <c r="N45" t="s">
         <v>5</v>
       </c>
-      <c r="P45">
+      <c r="P45" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q45">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>45</v>
       </c>
-      <c r="Q45" cm="1">
-        <f t="array" ref="Q45">_xlfn.XLOOKUP(
+      <c r="R45" cm="1">
+        <f t="array" ref="R45">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>220</v>
       </c>
@@ -6118,17 +6275,20 @@
       <c r="N46" t="s">
         <v>5</v>
       </c>
-      <c r="P46">
+      <c r="P46" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q46">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>46</v>
       </c>
-      <c r="Q46" cm="1">
-        <f t="array" ref="Q46">_xlfn.XLOOKUP(
+      <c r="R46" cm="1">
+        <f t="array" ref="R46">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>220</v>
       </c>
@@ -6168,17 +6328,20 @@
       <c r="N47" t="s">
         <v>5</v>
       </c>
-      <c r="P47">
+      <c r="P47" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q47">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>47</v>
       </c>
-      <c r="Q47" cm="1">
-        <f t="array" ref="Q47">_xlfn.XLOOKUP(
+      <c r="R47" cm="1">
+        <f t="array" ref="R47">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>220</v>
       </c>
@@ -6218,17 +6381,20 @@
       <c r="N48" t="s">
         <v>5</v>
       </c>
-      <c r="P48">
+      <c r="P48" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q48">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>48</v>
       </c>
-      <c r="Q48" cm="1">
-        <f t="array" ref="Q48">_xlfn.XLOOKUP(
+      <c r="R48" cm="1">
+        <f t="array" ref="R48">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>220</v>
       </c>
@@ -6268,17 +6434,20 @@
       <c r="N49" t="s">
         <v>5</v>
       </c>
-      <c r="P49">
+      <c r="P49" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q49">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>49</v>
       </c>
-      <c r="Q49" cm="1">
-        <f t="array" ref="Q49">_xlfn.XLOOKUP(
+      <c r="R49" cm="1">
+        <f t="array" ref="R49">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>220</v>
       </c>
@@ -6318,17 +6487,20 @@
       <c r="N50" t="s">
         <v>5</v>
       </c>
-      <c r="P50">
+      <c r="P50" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q50">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>50</v>
       </c>
-      <c r="Q50" cm="1">
-        <f t="array" ref="Q50">_xlfn.XLOOKUP(
+      <c r="R50" cm="1">
+        <f t="array" ref="R50">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>220</v>
       </c>
@@ -6368,17 +6540,20 @@
       <c r="N51" t="s">
         <v>5</v>
       </c>
-      <c r="P51">
+      <c r="P51" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q51">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>51</v>
       </c>
-      <c r="Q51" cm="1">
-        <f t="array" ref="Q51">_xlfn.XLOOKUP(
+      <c r="R51" cm="1">
+        <f t="array" ref="R51">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>220</v>
       </c>
@@ -6418,17 +6593,20 @@
       <c r="N52" t="s">
         <v>5</v>
       </c>
-      <c r="P52">
+      <c r="P52" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q52">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>52</v>
       </c>
-      <c r="Q52" cm="1">
-        <f t="array" ref="Q52">_xlfn.XLOOKUP(
+      <c r="R52" cm="1">
+        <f t="array" ref="R52">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>220</v>
       </c>
@@ -6468,17 +6646,20 @@
       <c r="N53" t="s">
         <v>5</v>
       </c>
-      <c r="P53">
+      <c r="P53" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q53">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>53</v>
       </c>
-      <c r="Q53" cm="1">
-        <f t="array" ref="Q53">_xlfn.XLOOKUP(
+      <c r="R53" cm="1">
+        <f t="array" ref="R53">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -6518,17 +6699,20 @@
       <c r="N54" t="s">
         <v>5</v>
       </c>
-      <c r="P54">
+      <c r="P54" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q54">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>54</v>
       </c>
-      <c r="Q54" cm="1">
-        <f t="array" ref="Q54">_xlfn.XLOOKUP(
+      <c r="R54" cm="1">
+        <f t="array" ref="R54">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>220</v>
       </c>
@@ -6568,17 +6752,20 @@
       <c r="N55" t="s">
         <v>5</v>
       </c>
-      <c r="P55">
+      <c r="P55" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q55">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>55</v>
       </c>
-      <c r="Q55" cm="1">
-        <f t="array" ref="Q55">_xlfn.XLOOKUP(
+      <c r="R55" cm="1">
+        <f t="array" ref="R55">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>220</v>
       </c>
@@ -6618,17 +6805,20 @@
       <c r="N56" t="s">
         <v>5</v>
       </c>
-      <c r="P56">
+      <c r="P56" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q56">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>56</v>
       </c>
-      <c r="Q56" cm="1">
-        <f t="array" ref="Q56">_xlfn.XLOOKUP(
+      <c r="R56" cm="1">
+        <f t="array" ref="R56">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>220</v>
       </c>
@@ -6668,17 +6858,20 @@
       <c r="N57" t="s">
         <v>5</v>
       </c>
-      <c r="P57">
+      <c r="P57" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q57">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>57</v>
       </c>
-      <c r="Q57" cm="1">
-        <f t="array" ref="Q57">_xlfn.XLOOKUP(
+      <c r="R57" cm="1">
+        <f t="array" ref="R57">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>220</v>
       </c>
@@ -6718,17 +6911,20 @@
       <c r="N58" t="s">
         <v>5</v>
       </c>
-      <c r="P58">
+      <c r="P58" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q58">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>58</v>
       </c>
-      <c r="Q58" cm="1">
-        <f t="array" ref="Q58">_xlfn.XLOOKUP(
+      <c r="R58" cm="1">
+        <f t="array" ref="R58">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>220</v>
       </c>
@@ -6768,17 +6964,20 @@
       <c r="N59" t="s">
         <v>5</v>
       </c>
-      <c r="P59">
+      <c r="P59" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q59">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>59</v>
       </c>
-      <c r="Q59" cm="1">
-        <f t="array" ref="Q59">_xlfn.XLOOKUP(
+      <c r="R59" cm="1">
+        <f t="array" ref="R59">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>220</v>
       </c>
@@ -6818,17 +7017,20 @@
       <c r="N60" t="s">
         <v>5</v>
       </c>
-      <c r="P60">
+      <c r="P60" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q60">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>60</v>
       </c>
-      <c r="Q60" cm="1">
-        <f t="array" ref="Q60">_xlfn.XLOOKUP(
+      <c r="R60" cm="1">
+        <f t="array" ref="R60">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>220</v>
       </c>
@@ -6868,17 +7070,20 @@
       <c r="N61" t="s">
         <v>5</v>
       </c>
-      <c r="P61">
+      <c r="P61" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q61">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>61</v>
       </c>
-      <c r="Q61" cm="1">
-        <f t="array" ref="Q61">_xlfn.XLOOKUP(
+      <c r="R61" cm="1">
+        <f t="array" ref="R61">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>220</v>
       </c>
@@ -6918,17 +7123,20 @@
       <c r="N62" t="s">
         <v>5</v>
       </c>
-      <c r="P62">
+      <c r="P62" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q62">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>62</v>
       </c>
-      <c r="Q62" cm="1">
-        <f t="array" ref="Q62">_xlfn.XLOOKUP(
+      <c r="R62" cm="1">
+        <f t="array" ref="R62">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>220</v>
       </c>
@@ -6968,17 +7176,20 @@
       <c r="N63" t="s">
         <v>5</v>
       </c>
-      <c r="P63">
+      <c r="P63" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q63">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>63</v>
       </c>
-      <c r="Q63" cm="1">
-        <f t="array" ref="Q63">_xlfn.XLOOKUP(
+      <c r="R63" cm="1">
+        <f t="array" ref="R63">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>220</v>
       </c>
@@ -7018,17 +7229,20 @@
       <c r="N64" t="s">
         <v>5</v>
       </c>
-      <c r="P64">
+      <c r="P64" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q64">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>64</v>
       </c>
-      <c r="Q64" cm="1">
-        <f t="array" ref="Q64">_xlfn.XLOOKUP(
+      <c r="R64" cm="1">
+        <f t="array" ref="R64">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>220</v>
       </c>
@@ -7068,17 +7282,20 @@
       <c r="N65" t="s">
         <v>5</v>
       </c>
-      <c r="P65">
+      <c r="P65" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q65">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>65</v>
       </c>
-      <c r="Q65" cm="1">
-        <f t="array" ref="Q65">_xlfn.XLOOKUP(
+      <c r="R65" cm="1">
+        <f t="array" ref="R65">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>220</v>
       </c>
@@ -7118,17 +7335,20 @@
       <c r="N66" t="s">
         <v>5</v>
       </c>
-      <c r="P66">
+      <c r="P66" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q66">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>66</v>
       </c>
-      <c r="Q66" cm="1">
-        <f t="array" ref="Q66">_xlfn.XLOOKUP(
+      <c r="R66" cm="1">
+        <f t="array" ref="R66">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>263</v>
       </c>
@@ -7168,17 +7388,20 @@
       <c r="N67" t="s">
         <v>107</v>
       </c>
-      <c r="P67">
+      <c r="P67" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q67">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>67</v>
       </c>
-      <c r="Q67" cm="1">
-        <f t="array" ref="Q67">_xlfn.XLOOKUP(
+      <c r="R67" cm="1">
+        <f t="array" ref="R67">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>263</v>
       </c>
@@ -7218,17 +7441,20 @@
       <c r="N68" t="s">
         <v>21</v>
       </c>
-      <c r="P68">
+      <c r="P68" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q68">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>68</v>
       </c>
-      <c r="Q68" cm="1">
-        <f t="array" ref="Q68">_xlfn.XLOOKUP(
+      <c r="R68" cm="1">
+        <f t="array" ref="R68">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>263</v>
       </c>
@@ -7268,17 +7494,20 @@
       <c r="N69" t="s">
         <v>21</v>
       </c>
-      <c r="P69">
+      <c r="P69" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q69">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>69</v>
       </c>
-      <c r="Q69" cm="1">
-        <f t="array" ref="Q69">_xlfn.XLOOKUP(
+      <c r="R69" cm="1">
+        <f t="array" ref="R69">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>263</v>
       </c>
@@ -7318,17 +7547,20 @@
       <c r="N70" t="s">
         <v>107</v>
       </c>
-      <c r="P70">
+      <c r="P70" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q70">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>70</v>
       </c>
-      <c r="Q70" cm="1">
-        <f t="array" ref="Q70">_xlfn.XLOOKUP(
+      <c r="R70" cm="1">
+        <f t="array" ref="R70">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>263</v>
       </c>
@@ -7368,17 +7600,20 @@
       <c r="N71" t="s">
         <v>21</v>
       </c>
-      <c r="P71">
+      <c r="P71" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q71">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>71</v>
       </c>
-      <c r="Q71" cm="1">
-        <f t="array" ref="Q71">_xlfn.XLOOKUP(
+      <c r="R71" cm="1">
+        <f t="array" ref="R71">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>263</v>
       </c>
@@ -7418,17 +7653,20 @@
       <c r="N72" t="s">
         <v>21</v>
       </c>
-      <c r="P72">
+      <c r="P72" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q72">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>72</v>
       </c>
-      <c r="Q72" cm="1">
-        <f t="array" ref="Q72">_xlfn.XLOOKUP(
+      <c r="R72" cm="1">
+        <f t="array" ref="R72">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>263</v>
       </c>
@@ -7468,17 +7706,20 @@
       <c r="N73" t="s">
         <v>107</v>
       </c>
-      <c r="P73">
+      <c r="P73" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q73">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>73</v>
       </c>
-      <c r="Q73" cm="1">
-        <f t="array" ref="Q73">_xlfn.XLOOKUP(
+      <c r="R73" cm="1">
+        <f t="array" ref="R73">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>263</v>
       </c>
@@ -7518,17 +7759,20 @@
       <c r="N74" t="s">
         <v>21</v>
       </c>
-      <c r="P74">
+      <c r="P74" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q74">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>74</v>
       </c>
-      <c r="Q74" cm="1">
-        <f t="array" ref="Q74">_xlfn.XLOOKUP(
+      <c r="R74" cm="1">
+        <f t="array" ref="R74">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>263</v>
       </c>
@@ -7568,17 +7812,20 @@
       <c r="N75" t="s">
         <v>21</v>
       </c>
-      <c r="P75">
+      <c r="P75" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q75">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>75</v>
       </c>
-      <c r="Q75" cm="1">
-        <f t="array" ref="Q75">_xlfn.XLOOKUP(
+      <c r="R75" cm="1">
+        <f t="array" ref="R75">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>263</v>
       </c>
@@ -7618,17 +7865,20 @@
       <c r="N76" t="s">
         <v>107</v>
       </c>
-      <c r="P76">
+      <c r="P76" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q76">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>76</v>
       </c>
-      <c r="Q76" cm="1">
-        <f t="array" ref="Q76">_xlfn.XLOOKUP(
+      <c r="R76" cm="1">
+        <f t="array" ref="R76">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>263</v>
       </c>
@@ -7668,17 +7918,20 @@
       <c r="N77" t="s">
         <v>21</v>
       </c>
-      <c r="P77">
+      <c r="P77" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q77">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>77</v>
       </c>
-      <c r="Q77" cm="1">
-        <f t="array" ref="Q77">_xlfn.XLOOKUP(
+      <c r="R77" cm="1">
+        <f t="array" ref="R77">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>263</v>
       </c>
@@ -7718,17 +7971,20 @@
       <c r="N78" t="s">
         <v>21</v>
       </c>
-      <c r="P78">
+      <c r="P78" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q78">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>78</v>
       </c>
-      <c r="Q78" cm="1">
-        <f t="array" ref="Q78">_xlfn.XLOOKUP(
+      <c r="R78" cm="1">
+        <f t="array" ref="R78">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>263</v>
       </c>
@@ -7768,17 +8024,20 @@
       <c r="N79" t="s">
         <v>107</v>
       </c>
-      <c r="P79">
+      <c r="P79" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q79">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>79</v>
       </c>
-      <c r="Q79" cm="1">
-        <f t="array" ref="Q79">_xlfn.XLOOKUP(
+      <c r="R79" cm="1">
+        <f t="array" ref="R79">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>263</v>
       </c>
@@ -7818,17 +8077,20 @@
       <c r="N80" t="s">
         <v>21</v>
       </c>
-      <c r="P80">
+      <c r="P80" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q80">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>80</v>
       </c>
-      <c r="Q80" cm="1">
-        <f t="array" ref="Q80">_xlfn.XLOOKUP(
+      <c r="R80" cm="1">
+        <f t="array" ref="R80">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>263</v>
       </c>
@@ -7868,17 +8130,20 @@
       <c r="N81" t="s">
         <v>21</v>
       </c>
-      <c r="P81">
+      <c r="P81" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q81">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>81</v>
       </c>
-      <c r="Q81" cm="1">
-        <f t="array" ref="Q81">_xlfn.XLOOKUP(
+      <c r="R81" cm="1">
+        <f t="array" ref="R81">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>263</v>
       </c>
@@ -7918,17 +8183,20 @@
       <c r="N82" t="s">
         <v>107</v>
       </c>
-      <c r="P82">
+      <c r="P82" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q82">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>82</v>
       </c>
-      <c r="Q82" cm="1">
-        <f t="array" ref="Q82">_xlfn.XLOOKUP(
+      <c r="R82" cm="1">
+        <f t="array" ref="R82">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>263</v>
       </c>
@@ -7968,17 +8236,20 @@
       <c r="N83" t="s">
         <v>21</v>
       </c>
-      <c r="P83">
+      <c r="P83" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q83">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>83</v>
       </c>
-      <c r="Q83" cm="1">
-        <f t="array" ref="Q83">_xlfn.XLOOKUP(
+      <c r="R83" cm="1">
+        <f t="array" ref="R83">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>263</v>
       </c>
@@ -8018,17 +8289,20 @@
       <c r="N84" t="s">
         <v>21</v>
       </c>
-      <c r="P84">
+      <c r="P84" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q84">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>84</v>
       </c>
-      <c r="Q84" cm="1">
-        <f t="array" ref="Q84">_xlfn.XLOOKUP(
+      <c r="R84" cm="1">
+        <f t="array" ref="R84">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
@@ -8068,17 +8342,20 @@
       <c r="N85" t="s">
         <v>107</v>
       </c>
-      <c r="P85">
+      <c r="P85" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q85">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>85</v>
       </c>
-      <c r="Q85" cm="1">
-        <f t="array" ref="Q85">_xlfn.XLOOKUP(
+      <c r="R85" cm="1">
+        <f t="array" ref="R85">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>263</v>
       </c>
@@ -8118,17 +8395,20 @@
       <c r="N86" t="s">
         <v>21</v>
       </c>
-      <c r="P86">
+      <c r="P86" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q86">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>86</v>
       </c>
-      <c r="Q86" cm="1">
-        <f t="array" ref="Q86">_xlfn.XLOOKUP(
+      <c r="R86" cm="1">
+        <f t="array" ref="R86">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>263</v>
       </c>
@@ -8168,17 +8448,20 @@
       <c r="N87" t="s">
         <v>21</v>
       </c>
-      <c r="P87">
+      <c r="P87" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q87">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>87</v>
       </c>
-      <c r="Q87" cm="1">
-        <f t="array" ref="Q87">_xlfn.XLOOKUP(
+      <c r="R87" cm="1">
+        <f t="array" ref="R87">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>263</v>
       </c>
@@ -8218,17 +8501,20 @@
       <c r="N88" t="s">
         <v>107</v>
       </c>
-      <c r="P88">
+      <c r="P88" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q88">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>88</v>
       </c>
-      <c r="Q88" cm="1">
-        <f t="array" ref="Q88">_xlfn.XLOOKUP(
+      <c r="R88" cm="1">
+        <f t="array" ref="R88">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>263</v>
       </c>
@@ -8268,17 +8554,20 @@
       <c r="N89" t="s">
         <v>21</v>
       </c>
-      <c r="P89">
+      <c r="P89" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q89">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>89</v>
       </c>
-      <c r="Q89" cm="1">
-        <f t="array" ref="Q89">_xlfn.XLOOKUP(
+      <c r="R89" cm="1">
+        <f t="array" ref="R89">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>263</v>
       </c>
@@ -8318,17 +8607,20 @@
       <c r="N90" t="s">
         <v>21</v>
       </c>
-      <c r="P90">
+      <c r="P90" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q90">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>90</v>
       </c>
-      <c r="Q90" cm="1">
-        <f t="array" ref="Q90">_xlfn.XLOOKUP(
+      <c r="R90" cm="1">
+        <f t="array" ref="R90">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>263</v>
       </c>
@@ -8368,17 +8660,20 @@
       <c r="N91" t="s">
         <v>21</v>
       </c>
-      <c r="P91">
+      <c r="P91" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q91">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>91</v>
       </c>
-      <c r="Q91" cm="1">
-        <f t="array" ref="Q91">_xlfn.XLOOKUP(
+      <c r="R91" cm="1">
+        <f t="array" ref="R91">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>263</v>
       </c>
@@ -8418,17 +8713,20 @@
       <c r="N92" t="s">
         <v>21</v>
       </c>
-      <c r="P92">
+      <c r="P92" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q92">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>92</v>
       </c>
-      <c r="Q92" cm="1">
-        <f t="array" ref="Q92">_xlfn.XLOOKUP(
+      <c r="R92" cm="1">
+        <f t="array" ref="R92">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>263</v>
       </c>
@@ -8468,17 +8766,20 @@
       <c r="N93" t="s">
         <v>21</v>
       </c>
-      <c r="P93">
+      <c r="P93" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q93">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>93</v>
       </c>
-      <c r="Q93" cm="1">
-        <f t="array" ref="Q93">_xlfn.XLOOKUP(
+      <c r="R93" cm="1">
+        <f t="array" ref="R93">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>263</v>
       </c>
@@ -8518,17 +8819,20 @@
       <c r="N94" t="s">
         <v>21</v>
       </c>
-      <c r="P94">
+      <c r="P94" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q94">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>94</v>
       </c>
-      <c r="Q94" cm="1">
-        <f t="array" ref="Q94">_xlfn.XLOOKUP(
+      <c r="R94" cm="1">
+        <f t="array" ref="R94">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>263</v>
       </c>
@@ -8568,17 +8872,20 @@
       <c r="N95" t="s">
         <v>21</v>
       </c>
-      <c r="P95">
+      <c r="P95" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q95">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>95</v>
       </c>
-      <c r="Q95" cm="1">
-        <f t="array" ref="Q95">_xlfn.XLOOKUP(
+      <c r="R95" cm="1">
+        <f t="array" ref="R95">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>263</v>
       </c>
@@ -8618,17 +8925,20 @@
       <c r="N96" t="s">
         <v>21</v>
       </c>
-      <c r="P96">
+      <c r="P96" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q96">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>96</v>
       </c>
-      <c r="Q96" cm="1">
-        <f t="array" ref="Q96">_xlfn.XLOOKUP(
+      <c r="R96" cm="1">
+        <f t="array" ref="R96">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>263</v>
       </c>
@@ -8668,17 +8978,20 @@
       <c r="N97" t="s">
         <v>21</v>
       </c>
-      <c r="P97">
+      <c r="P97" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q97">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>97</v>
       </c>
-      <c r="Q97" cm="1">
-        <f t="array" ref="Q97">_xlfn.XLOOKUP(
+      <c r="R97" cm="1">
+        <f t="array" ref="R97">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>263</v>
       </c>
@@ -8718,17 +9031,20 @@
       <c r="N98" t="s">
         <v>21</v>
       </c>
-      <c r="P98">
+      <c r="P98" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q98">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>98</v>
       </c>
-      <c r="Q98" cm="1">
-        <f t="array" ref="Q98">_xlfn.XLOOKUP(
+      <c r="R98" cm="1">
+        <f t="array" ref="R98">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>263</v>
       </c>
@@ -8768,17 +9084,20 @@
       <c r="N99" t="s">
         <v>107</v>
       </c>
-      <c r="P99">
+      <c r="P99" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q99">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>99</v>
       </c>
-      <c r="Q99" cm="1">
-        <f t="array" ref="Q99">_xlfn.XLOOKUP(
+      <c r="R99" cm="1">
+        <f t="array" ref="R99">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>263</v>
       </c>
@@ -8818,17 +9137,20 @@
       <c r="N100" t="s">
         <v>21</v>
       </c>
-      <c r="P100">
+      <c r="P100" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q100">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>100</v>
       </c>
-      <c r="Q100" cm="1">
-        <f t="array" ref="Q100">_xlfn.XLOOKUP(
+      <c r="R100" cm="1">
+        <f t="array" ref="R100">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>263</v>
       </c>
@@ -8868,17 +9190,20 @@
       <c r="N101" t="s">
         <v>21</v>
       </c>
-      <c r="P101">
+      <c r="P101" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q101">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>101</v>
       </c>
-      <c r="Q101" cm="1">
-        <f t="array" ref="Q101">_xlfn.XLOOKUP(
+      <c r="R101" cm="1">
+        <f t="array" ref="R101">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>263</v>
       </c>
@@ -8918,17 +9243,20 @@
       <c r="N102" t="s">
         <v>107</v>
       </c>
-      <c r="P102">
+      <c r="P102" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q102">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>102</v>
       </c>
-      <c r="Q102" cm="1">
-        <f t="array" ref="Q102">_xlfn.XLOOKUP(
+      <c r="R102" cm="1">
+        <f t="array" ref="R102">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>263</v>
       </c>
@@ -8968,17 +9296,20 @@
       <c r="N103" t="s">
         <v>21</v>
       </c>
-      <c r="P103">
+      <c r="P103" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q103">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>103</v>
       </c>
-      <c r="Q103" cm="1">
-        <f t="array" ref="Q103">_xlfn.XLOOKUP(
+      <c r="R103" cm="1">
+        <f t="array" ref="R103">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>263</v>
       </c>
@@ -9018,17 +9349,20 @@
       <c r="N104" t="s">
         <v>21</v>
       </c>
-      <c r="P104">
+      <c r="P104" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q104">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>104</v>
       </c>
-      <c r="Q104" cm="1">
-        <f t="array" ref="Q104">_xlfn.XLOOKUP(
+      <c r="R104" cm="1">
+        <f t="array" ref="R104">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>263</v>
       </c>
@@ -9068,17 +9402,20 @@
       <c r="N105" t="s">
         <v>107</v>
       </c>
-      <c r="P105">
+      <c r="P105" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q105">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>105</v>
       </c>
-      <c r="Q105" cm="1">
-        <f t="array" ref="Q105">_xlfn.XLOOKUP(
+      <c r="R105" cm="1">
+        <f t="array" ref="R105">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>263</v>
       </c>
@@ -9118,17 +9455,20 @@
       <c r="N106" t="s">
         <v>21</v>
       </c>
-      <c r="P106">
+      <c r="P106" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q106">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>106</v>
       </c>
-      <c r="Q106" cm="1">
-        <f t="array" ref="Q106">_xlfn.XLOOKUP(
+      <c r="R106" cm="1">
+        <f t="array" ref="R106">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>263</v>
       </c>
@@ -9168,17 +9508,20 @@
       <c r="N107" t="s">
         <v>21</v>
       </c>
-      <c r="P107">
+      <c r="P107" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q107">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>107</v>
       </c>
-      <c r="Q107" cm="1">
-        <f t="array" ref="Q107">_xlfn.XLOOKUP(
+      <c r="R107" cm="1">
+        <f t="array" ref="R107">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>263</v>
       </c>
@@ -9218,17 +9561,20 @@
       <c r="N108" t="s">
         <v>107</v>
       </c>
-      <c r="P108">
+      <c r="P108" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q108">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>108</v>
       </c>
-      <c r="Q108" cm="1">
-        <f t="array" ref="Q108">_xlfn.XLOOKUP(
+      <c r="R108" cm="1">
+        <f t="array" ref="R108">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>263</v>
       </c>
@@ -9268,17 +9614,20 @@
       <c r="N109" t="s">
         <v>21</v>
       </c>
-      <c r="P109">
+      <c r="P109" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q109">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>109</v>
       </c>
-      <c r="Q109" cm="1">
-        <f t="array" ref="Q109">_xlfn.XLOOKUP(
+      <c r="R109" cm="1">
+        <f t="array" ref="R109">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>263</v>
       </c>
@@ -9318,17 +9667,20 @@
       <c r="N110" t="s">
         <v>21</v>
       </c>
-      <c r="P110">
+      <c r="P110" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q110">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>110</v>
       </c>
-      <c r="Q110" cm="1">
-        <f t="array" ref="Q110">_xlfn.XLOOKUP(
+      <c r="R110" cm="1">
+        <f t="array" ref="R110">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>328</v>
       </c>
@@ -9368,17 +9720,20 @@
       <c r="N111" t="s">
         <v>5</v>
       </c>
-      <c r="P111">
+      <c r="P111" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q111">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>111</v>
       </c>
-      <c r="Q111" cm="1">
-        <f t="array" ref="Q111">_xlfn.XLOOKUP(
+      <c r="R111" cm="1">
+        <f t="array" ref="R111">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>111</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>328</v>
       </c>
@@ -9418,17 +9773,20 @@
       <c r="N112" t="s">
         <v>5</v>
       </c>
-      <c r="P112">
+      <c r="P112" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q112">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>112</v>
       </c>
-      <c r="Q112" cm="1">
-        <f t="array" ref="Q112">_xlfn.XLOOKUP(
+      <c r="R112" cm="1">
+        <f t="array" ref="R112">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>328</v>
       </c>
@@ -9468,17 +9826,20 @@
       <c r="N113" t="s">
         <v>107</v>
       </c>
-      <c r="P113">
+      <c r="P113" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q113">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>113</v>
       </c>
-      <c r="Q113" cm="1">
-        <f t="array" ref="Q113">_xlfn.XLOOKUP(
+      <c r="R113" cm="1">
+        <f t="array" ref="R113">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>113</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>328</v>
       </c>
@@ -9518,17 +9879,20 @@
       <c r="N114" t="s">
         <v>107</v>
       </c>
-      <c r="P114">
+      <c r="P114" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q114">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>114</v>
       </c>
-      <c r="Q114" cm="1">
-        <f t="array" ref="Q114">_xlfn.XLOOKUP(
+      <c r="R114" cm="1">
+        <f t="array" ref="R114">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>328</v>
       </c>
@@ -9568,17 +9932,20 @@
       <c r="N115" t="s">
         <v>5</v>
       </c>
-      <c r="P115">
+      <c r="P115" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q115">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>115</v>
       </c>
-      <c r="Q115" cm="1">
-        <f t="array" ref="Q115">_xlfn.XLOOKUP(
+      <c r="R115" cm="1">
+        <f t="array" ref="R115">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>115</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>328</v>
       </c>
@@ -9618,17 +9985,20 @@
       <c r="N116" t="s">
         <v>5</v>
       </c>
-      <c r="P116">
+      <c r="P116" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q116">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>116</v>
       </c>
-      <c r="Q116" cm="1">
-        <f t="array" ref="Q116">_xlfn.XLOOKUP(
+      <c r="R116" cm="1">
+        <f t="array" ref="R116">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>328</v>
       </c>
@@ -9668,17 +10038,20 @@
       <c r="N117" t="s">
         <v>107</v>
       </c>
-      <c r="P117">
+      <c r="P117" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q117">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>117</v>
       </c>
-      <c r="Q117" cm="1">
-        <f t="array" ref="Q117">_xlfn.XLOOKUP(
+      <c r="R117" cm="1">
+        <f t="array" ref="R117">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>328</v>
       </c>
@@ -9718,17 +10091,20 @@
       <c r="N118" t="s">
         <v>107</v>
       </c>
-      <c r="P118">
+      <c r="P118" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q118">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>118</v>
       </c>
-      <c r="Q118" cm="1">
-        <f t="array" ref="Q118">_xlfn.XLOOKUP(
+      <c r="R118" cm="1">
+        <f t="array" ref="R118">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>118</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>328</v>
       </c>
@@ -9768,17 +10144,20 @@
       <c r="N119" t="s">
         <v>5</v>
       </c>
-      <c r="P119">
+      <c r="P119" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q119">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>119</v>
       </c>
-      <c r="Q119" cm="1">
-        <f t="array" ref="Q119">_xlfn.XLOOKUP(
+      <c r="R119" cm="1">
+        <f t="array" ref="R119">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>119</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>328</v>
       </c>
@@ -9818,17 +10197,20 @@
       <c r="N120" t="s">
         <v>5</v>
       </c>
-      <c r="P120">
+      <c r="P120" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q120">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>120</v>
       </c>
-      <c r="Q120" cm="1">
-        <f t="array" ref="Q120">_xlfn.XLOOKUP(
+      <c r="R120" cm="1">
+        <f t="array" ref="R120">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>328</v>
       </c>
@@ -9868,17 +10250,20 @@
       <c r="N121" t="s">
         <v>107</v>
       </c>
-      <c r="P121">
+      <c r="P121" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q121">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>121</v>
       </c>
-      <c r="Q121" cm="1">
-        <f t="array" ref="Q121">_xlfn.XLOOKUP(
+      <c r="R121" cm="1">
+        <f t="array" ref="R121">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>121</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>328</v>
       </c>
@@ -9918,17 +10303,20 @@
       <c r="N122" t="s">
         <v>107</v>
       </c>
-      <c r="P122">
+      <c r="P122" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q122">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>122</v>
       </c>
-      <c r="Q122" cm="1">
-        <f t="array" ref="Q122">_xlfn.XLOOKUP(
+      <c r="R122" cm="1">
+        <f t="array" ref="R122">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>328</v>
       </c>
@@ -9968,17 +10356,20 @@
       <c r="N123" t="s">
         <v>5</v>
       </c>
-      <c r="P123">
+      <c r="P123" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q123">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>123</v>
       </c>
-      <c r="Q123" cm="1">
-        <f t="array" ref="Q123">_xlfn.XLOOKUP(
+      <c r="R123" cm="1">
+        <f t="array" ref="R123">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>328</v>
       </c>
@@ -10018,17 +10409,20 @@
       <c r="N124" t="s">
         <v>5</v>
       </c>
-      <c r="P124">
+      <c r="P124" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q124">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>124</v>
       </c>
-      <c r="Q124" cm="1">
-        <f t="array" ref="Q124">_xlfn.XLOOKUP(
+      <c r="R124" cm="1">
+        <f t="array" ref="R124">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>124</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>328</v>
       </c>
@@ -10068,17 +10462,20 @@
       <c r="N125" t="s">
         <v>107</v>
       </c>
-      <c r="P125">
+      <c r="P125" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q125">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>125</v>
       </c>
-      <c r="Q125" cm="1">
-        <f t="array" ref="Q125">_xlfn.XLOOKUP(
+      <c r="R125" cm="1">
+        <f t="array" ref="R125">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>125</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>328</v>
       </c>
@@ -10118,17 +10515,20 @@
       <c r="N126" t="s">
         <v>107</v>
       </c>
-      <c r="P126">
+      <c r="P126" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q126">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>126</v>
       </c>
-      <c r="Q126" cm="1">
-        <f t="array" ref="Q126">_xlfn.XLOOKUP(
+      <c r="R126" cm="1">
+        <f t="array" ref="R126">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>371</v>
       </c>
@@ -10168,17 +10568,20 @@
       <c r="N127" t="s">
         <v>5</v>
       </c>
-      <c r="P127">
+      <c r="P127" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q127">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>127</v>
       </c>
-      <c r="Q127" cm="1">
-        <f t="array" ref="Q127">_xlfn.XLOOKUP(
+      <c r="R127" cm="1">
+        <f t="array" ref="R127">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>127</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>371</v>
       </c>
@@ -10218,17 +10621,20 @@
       <c r="N128" t="s">
         <v>107</v>
       </c>
-      <c r="P128">
+      <c r="P128" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q128">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>128</v>
       </c>
-      <c r="Q128" cm="1">
-        <f t="array" ref="Q128">_xlfn.XLOOKUP(
+      <c r="R128" cm="1">
+        <f t="array" ref="R128">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>128</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>371</v>
       </c>
@@ -10268,17 +10674,20 @@
       <c r="N129" t="s">
         <v>5</v>
       </c>
-      <c r="P129">
+      <c r="P129" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q129">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>129</v>
       </c>
-      <c r="Q129" cm="1">
-        <f t="array" ref="Q129">_xlfn.XLOOKUP(
+      <c r="R129" cm="1">
+        <f t="array" ref="R129">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>129</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>371</v>
       </c>
@@ -10318,17 +10727,20 @@
       <c r="N130" t="s">
         <v>5</v>
       </c>
-      <c r="P130">
+      <c r="P130" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q130">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>130</v>
       </c>
-      <c r="Q130" cm="1">
-        <f t="array" ref="Q130">_xlfn.XLOOKUP(
+      <c r="R130" cm="1">
+        <f t="array" ref="R130">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>371</v>
       </c>
@@ -10368,17 +10780,20 @@
       <c r="N131" t="s">
         <v>107</v>
       </c>
-      <c r="P131">
+      <c r="P131" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q131">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>131</v>
       </c>
-      <c r="Q131" cm="1">
-        <f t="array" ref="Q131">_xlfn.XLOOKUP(
+      <c r="R131" cm="1">
+        <f t="array" ref="R131">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>131</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>371</v>
       </c>
@@ -10418,17 +10833,20 @@
       <c r="N132" t="s">
         <v>107</v>
       </c>
-      <c r="P132">
+      <c r="P132" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q132">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>132</v>
       </c>
-      <c r="Q132" cm="1">
-        <f t="array" ref="Q132">_xlfn.XLOOKUP(
+      <c r="R132" cm="1">
+        <f t="array" ref="R132">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>132</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>371</v>
       </c>
@@ -10468,17 +10886,20 @@
       <c r="N133" t="s">
         <v>5</v>
       </c>
-      <c r="P133">
+      <c r="P133" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q133">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>133</v>
       </c>
-      <c r="Q133" cm="1">
-        <f t="array" ref="Q133">_xlfn.XLOOKUP(
+      <c r="R133" cm="1">
+        <f t="array" ref="R133">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>133</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>371</v>
       </c>
@@ -10518,17 +10939,20 @@
       <c r="N134" t="s">
         <v>5</v>
       </c>
-      <c r="P134">
+      <c r="P134" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q134">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>134</v>
       </c>
-      <c r="Q134" cm="1">
-        <f t="array" ref="Q134">_xlfn.XLOOKUP(
+      <c r="R134" cm="1">
+        <f t="array" ref="R134">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>371</v>
       </c>
@@ -10568,17 +10992,20 @@
       <c r="N135" t="s">
         <v>107</v>
       </c>
-      <c r="P135">
+      <c r="P135" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q135">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>135</v>
       </c>
-      <c r="Q135" cm="1">
-        <f t="array" ref="Q135">_xlfn.XLOOKUP(
+      <c r="R135" cm="1">
+        <f t="array" ref="R135">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>371</v>
       </c>
@@ -10618,17 +11045,20 @@
       <c r="N136" t="s">
         <v>107</v>
       </c>
-      <c r="P136">
+      <c r="P136" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q136">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>136</v>
       </c>
-      <c r="Q136" cm="1">
-        <f t="array" ref="Q136">_xlfn.XLOOKUP(
+      <c r="R136" cm="1">
+        <f t="array" ref="R136">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>371</v>
       </c>
@@ -10668,17 +11098,20 @@
       <c r="N137" t="s">
         <v>5</v>
       </c>
-      <c r="P137">
+      <c r="P137" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q137">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>137</v>
       </c>
-      <c r="Q137" cm="1">
-        <f t="array" ref="Q137">_xlfn.XLOOKUP(
+      <c r="R137" cm="1">
+        <f t="array" ref="R137">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>371</v>
       </c>
@@ -10718,17 +11151,20 @@
       <c r="N138" t="s">
         <v>5</v>
       </c>
-      <c r="P138">
+      <c r="P138" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q138">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>138</v>
       </c>
-      <c r="Q138" cm="1">
-        <f t="array" ref="Q138">_xlfn.XLOOKUP(
+      <c r="R138" cm="1">
+        <f t="array" ref="R138">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>414</v>
       </c>
@@ -10768,17 +11204,20 @@
       <c r="N139" t="s">
         <v>5</v>
       </c>
-      <c r="P139">
+      <c r="P139" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q139">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>139</v>
       </c>
-      <c r="Q139" cm="1">
-        <f t="array" ref="Q139">_xlfn.XLOOKUP(
+      <c r="R139" cm="1">
+        <f t="array" ref="R139">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>139</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>414</v>
       </c>
@@ -10818,17 +11257,20 @@
       <c r="N140" t="s">
         <v>5</v>
       </c>
-      <c r="P140">
+      <c r="P140" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q140">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>140</v>
       </c>
-      <c r="Q140" cm="1">
-        <f t="array" ref="Q140">_xlfn.XLOOKUP(
+      <c r="R140" cm="1">
+        <f t="array" ref="R140">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>414</v>
       </c>
@@ -10868,17 +11310,20 @@
       <c r="N141" t="s">
         <v>107</v>
       </c>
-      <c r="P141">
+      <c r="P141" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q141">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>141</v>
       </c>
-      <c r="Q141" cm="1">
-        <f t="array" ref="Q141">_xlfn.XLOOKUP(
+      <c r="R141" cm="1">
+        <f t="array" ref="R141">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>414</v>
       </c>
@@ -10918,17 +11363,20 @@
       <c r="N142" t="s">
         <v>107</v>
       </c>
-      <c r="P142">
+      <c r="P142" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q142">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>142</v>
       </c>
-      <c r="Q142" cm="1">
-        <f t="array" ref="Q142">_xlfn.XLOOKUP(
+      <c r="R142" cm="1">
+        <f t="array" ref="R142">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>414</v>
       </c>
@@ -10968,17 +11416,20 @@
       <c r="N143" t="s">
         <v>5</v>
       </c>
-      <c r="P143">
+      <c r="P143" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q143">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>143</v>
       </c>
-      <c r="Q143" cm="1">
-        <f t="array" ref="Q143">_xlfn.XLOOKUP(
+      <c r="R143" cm="1">
+        <f t="array" ref="R143">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>143</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>414</v>
       </c>
@@ -11018,17 +11469,20 @@
       <c r="N144" t="s">
         <v>107</v>
       </c>
-      <c r="P144">
+      <c r="P144" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q144">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>144</v>
       </c>
-      <c r="Q144" cm="1">
-        <f t="array" ref="Q144">_xlfn.XLOOKUP(
+      <c r="R144" cm="1">
+        <f t="array" ref="R144">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>414</v>
       </c>
@@ -11068,17 +11522,20 @@
       <c r="N145" t="s">
         <v>5</v>
       </c>
-      <c r="P145">
+      <c r="P145" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q145">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>145</v>
       </c>
-      <c r="Q145" cm="1">
-        <f t="array" ref="Q145">_xlfn.XLOOKUP(
+      <c r="R145" cm="1">
+        <f t="array" ref="R145">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>414</v>
       </c>
@@ -11118,17 +11575,20 @@
       <c r="N146" t="s">
         <v>5</v>
       </c>
-      <c r="P146">
+      <c r="P146" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q146">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>146</v>
       </c>
-      <c r="Q146" cm="1">
-        <f t="array" ref="Q146">_xlfn.XLOOKUP(
+      <c r="R146" cm="1">
+        <f t="array" ref="R146">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>414</v>
       </c>
@@ -11168,17 +11628,20 @@
       <c r="N147" t="s">
         <v>107</v>
       </c>
-      <c r="P147">
+      <c r="P147" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q147">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>147</v>
       </c>
-      <c r="Q147" cm="1">
-        <f t="array" ref="Q147">_xlfn.XLOOKUP(
+      <c r="R147" cm="1">
+        <f t="array" ref="R147">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>414</v>
       </c>
@@ -11218,17 +11681,20 @@
       <c r="N148" t="s">
         <v>107</v>
       </c>
-      <c r="P148">
+      <c r="P148" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q148">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>148</v>
       </c>
-      <c r="Q148" cm="1">
-        <f t="array" ref="Q148">_xlfn.XLOOKUP(
+      <c r="R148" cm="1">
+        <f t="array" ref="R148">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>414</v>
       </c>
@@ -11268,17 +11734,20 @@
       <c r="N149" t="s">
         <v>5</v>
       </c>
-      <c r="P149">
+      <c r="P149" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q149">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>149</v>
       </c>
-      <c r="Q149" cm="1">
-        <f t="array" ref="Q149">_xlfn.XLOOKUP(
+      <c r="R149" cm="1">
+        <f t="array" ref="R149">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>149</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>414</v>
       </c>
@@ -11318,17 +11787,20 @@
       <c r="N150" t="s">
         <v>5</v>
       </c>
-      <c r="P150">
+      <c r="P150" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q150">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>150</v>
       </c>
-      <c r="Q150" cm="1">
-        <f t="array" ref="Q150">_xlfn.XLOOKUP(
+      <c r="R150" cm="1">
+        <f t="array" ref="R150">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>153</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>414</v>
       </c>
@@ -11368,17 +11840,20 @@
       <c r="N151" t="s">
         <v>107</v>
       </c>
-      <c r="P151">
+      <c r="P151" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q151">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>151</v>
       </c>
-      <c r="Q151" cm="1">
-        <f t="array" ref="Q151">_xlfn.XLOOKUP(
+      <c r="R151" cm="1">
+        <f t="array" ref="R151">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>151</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>414</v>
       </c>
@@ -11418,17 +11893,20 @@
       <c r="N152" t="s">
         <v>107</v>
       </c>
-      <c r="P152">
+      <c r="P152" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q152">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>152</v>
       </c>
-      <c r="Q152" cm="1">
-        <f t="array" ref="Q152">_xlfn.XLOOKUP(
+      <c r="R152" cm="1">
+        <f t="array" ref="R152">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>154</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>414</v>
       </c>
@@ -11468,17 +11946,20 @@
       <c r="N153" t="s">
         <v>5</v>
       </c>
-      <c r="P153">
+      <c r="P153" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q153">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>153</v>
       </c>
-      <c r="Q153" cm="1">
-        <f t="array" ref="Q153">_xlfn.XLOOKUP(
+      <c r="R153" cm="1">
+        <f t="array" ref="R153">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>153</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>414</v>
       </c>
@@ -11518,17 +11999,20 @@
       <c r="N154" t="s">
         <v>107</v>
       </c>
-      <c r="P154">
+      <c r="P154" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q154">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>154</v>
       </c>
-      <c r="Q154" cm="1">
-        <f t="array" ref="Q154">_xlfn.XLOOKUP(
+      <c r="R154" cm="1">
+        <f t="array" ref="R154">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>414</v>
       </c>
@@ -11568,17 +12052,20 @@
       <c r="N155" t="s">
         <v>5</v>
       </c>
-      <c r="P155">
+      <c r="P155" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q155">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>155</v>
       </c>
-      <c r="Q155" cm="1">
-        <f t="array" ref="Q155">_xlfn.XLOOKUP(
+      <c r="R155" cm="1">
+        <f t="array" ref="R155">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>155</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>414</v>
       </c>
@@ -11618,17 +12105,20 @@
       <c r="N156" t="s">
         <v>5</v>
       </c>
-      <c r="P156">
+      <c r="P156" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q156">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>156</v>
       </c>
-      <c r="Q156" cm="1">
-        <f t="array" ref="Q156">_xlfn.XLOOKUP(
+      <c r="R156" cm="1">
+        <f t="array" ref="R156">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>156</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>414</v>
       </c>
@@ -11668,17 +12158,20 @@
       <c r="N157" t="s">
         <v>107</v>
       </c>
-      <c r="P157">
+      <c r="P157" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q157">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>157</v>
       </c>
-      <c r="Q157" cm="1">
-        <f t="array" ref="Q157">_xlfn.XLOOKUP(
+      <c r="R157" cm="1">
+        <f t="array" ref="R157">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>157</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>414</v>
       </c>
@@ -11718,17 +12211,20 @@
       <c r="N158" t="s">
         <v>107</v>
       </c>
-      <c r="P158">
+      <c r="P158" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q158">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>158</v>
       </c>
-      <c r="Q158" cm="1">
-        <f t="array" ref="Q158">_xlfn.XLOOKUP(
+      <c r="R158" cm="1">
+        <f t="array" ref="R158">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>158</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>414</v>
       </c>
@@ -11768,17 +12264,20 @@
       <c r="N159" t="s">
         <v>5</v>
       </c>
-      <c r="P159">
+      <c r="P159" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q159">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>159</v>
       </c>
-      <c r="Q159" cm="1">
-        <f t="array" ref="Q159">_xlfn.XLOOKUP(
+      <c r="R159" cm="1">
+        <f t="array" ref="R159">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>159</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>414</v>
       </c>
@@ -11818,17 +12317,20 @@
       <c r="N160" t="s">
         <v>107</v>
       </c>
-      <c r="P160">
+      <c r="P160" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q160">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>160</v>
       </c>
-      <c r="Q160" cm="1">
-        <f t="array" ref="Q160">_xlfn.XLOOKUP(
+      <c r="R160" cm="1">
+        <f t="array" ref="R160">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>160</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>457</v>
       </c>
@@ -11868,17 +12370,20 @@
       <c r="N161" t="s">
         <v>5</v>
       </c>
-      <c r="P161">
+      <c r="P161" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q161">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>161</v>
       </c>
-      <c r="Q161" cm="1">
-        <f t="array" ref="Q161">_xlfn.XLOOKUP(
+      <c r="R161" cm="1">
+        <f t="array" ref="R161">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>169</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>457</v>
       </c>
@@ -11918,17 +12423,20 @@
       <c r="N162" t="s">
         <v>5</v>
       </c>
-      <c r="P162">
+      <c r="P162" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q162">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>162</v>
       </c>
-      <c r="Q162" cm="1">
-        <f t="array" ref="Q162">_xlfn.XLOOKUP(
+      <c r="R162" cm="1">
+        <f t="array" ref="R162">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>170</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>457</v>
       </c>
@@ -11968,17 +12476,20 @@
       <c r="N163" t="s">
         <v>21</v>
       </c>
-      <c r="P163">
+      <c r="P163" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q163">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>163</v>
       </c>
-      <c r="Q163" cm="1">
-        <f t="array" ref="Q163">_xlfn.XLOOKUP(
+      <c r="R163" cm="1">
+        <f t="array" ref="R163">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>171</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>457</v>
       </c>
@@ -12018,17 +12529,20 @@
       <c r="N164" t="s">
         <v>21</v>
       </c>
-      <c r="P164">
+      <c r="P164" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q164">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>164</v>
       </c>
-      <c r="Q164" cm="1">
-        <f t="array" ref="Q164">_xlfn.XLOOKUP(
+      <c r="R164" cm="1">
+        <f t="array" ref="R164">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>172</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>457</v>
       </c>
@@ -12068,17 +12582,20 @@
       <c r="N165" t="s">
         <v>5</v>
       </c>
-      <c r="P165">
+      <c r="P165" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q165">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>165</v>
       </c>
-      <c r="Q165" cm="1">
-        <f t="array" ref="Q165">_xlfn.XLOOKUP(
+      <c r="R165" cm="1">
+        <f t="array" ref="R165">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>165</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>457</v>
       </c>
@@ -12118,17 +12635,20 @@
       <c r="N166" t="s">
         <v>5</v>
       </c>
-      <c r="P166">
+      <c r="P166" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q166">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>166</v>
       </c>
-      <c r="Q166" cm="1">
-        <f t="array" ref="Q166">_xlfn.XLOOKUP(
+      <c r="R166" cm="1">
+        <f t="array" ref="R166">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>166</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>457</v>
       </c>
@@ -12168,17 +12688,20 @@
       <c r="N167" t="s">
         <v>21</v>
       </c>
-      <c r="P167">
+      <c r="P167" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q167">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>167</v>
       </c>
-      <c r="Q167" cm="1">
-        <f t="array" ref="Q167">_xlfn.XLOOKUP(
+      <c r="R167" cm="1">
+        <f t="array" ref="R167">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>167</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>457</v>
       </c>
@@ -12218,17 +12741,20 @@
       <c r="N168" t="s">
         <v>21</v>
       </c>
-      <c r="P168">
+      <c r="P168" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q168">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>168</v>
       </c>
-      <c r="Q168" cm="1">
-        <f t="array" ref="Q168">_xlfn.XLOOKUP(
+      <c r="R168" cm="1">
+        <f t="array" ref="R168">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>457</v>
       </c>
@@ -12268,17 +12794,20 @@
       <c r="N169" t="s">
         <v>5</v>
       </c>
-      <c r="P169">
+      <c r="P169" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q169">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>169</v>
       </c>
-      <c r="Q169" cm="1">
-        <f t="array" ref="Q169">_xlfn.XLOOKUP(
+      <c r="R169" cm="1">
+        <f t="array" ref="R169">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>169</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>457</v>
       </c>
@@ -12318,17 +12847,20 @@
       <c r="N170" t="s">
         <v>5</v>
       </c>
-      <c r="P170">
+      <c r="P170" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q170">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>170</v>
       </c>
-      <c r="Q170" cm="1">
-        <f t="array" ref="Q170">_xlfn.XLOOKUP(
+      <c r="R170" cm="1">
+        <f t="array" ref="R170">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>170</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>457</v>
       </c>
@@ -12368,17 +12900,20 @@
       <c r="N171" t="s">
         <v>21</v>
       </c>
-      <c r="P171">
+      <c r="P171" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q171">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>171</v>
       </c>
-      <c r="Q171" cm="1">
-        <f t="array" ref="Q171">_xlfn.XLOOKUP(
+      <c r="R171" cm="1">
+        <f t="array" ref="R171">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>171</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>457</v>
       </c>
@@ -12418,17 +12953,20 @@
       <c r="N172" t="s">
         <v>21</v>
       </c>
-      <c r="P172">
+      <c r="P172" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q172">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>172</v>
       </c>
-      <c r="Q172" cm="1">
-        <f t="array" ref="Q172">_xlfn.XLOOKUP(
+      <c r="R172" cm="1">
+        <f t="array" ref="R172">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>172</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>457</v>
       </c>
@@ -12468,17 +13006,20 @@
       <c r="N173" t="s">
         <v>5</v>
       </c>
-      <c r="P173">
+      <c r="P173" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q173">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>173</v>
       </c>
-      <c r="Q173" cm="1">
-        <f t="array" ref="Q173">_xlfn.XLOOKUP(
+      <c r="R173" cm="1">
+        <f t="array" ref="R173">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>173</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>457</v>
       </c>
@@ -12518,17 +13059,20 @@
       <c r="N174" t="s">
         <v>5</v>
       </c>
-      <c r="P174">
+      <c r="P174" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q174">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>174</v>
       </c>
-      <c r="Q174" cm="1">
-        <f t="array" ref="Q174">_xlfn.XLOOKUP(
+      <c r="R174" cm="1">
+        <f t="array" ref="R174">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>210</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>457</v>
       </c>
@@ -12568,17 +13112,20 @@
       <c r="N175" t="s">
         <v>21</v>
       </c>
-      <c r="P175">
+      <c r="P175" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q175">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>175</v>
       </c>
-      <c r="Q175" cm="1">
-        <f t="array" ref="Q175">_xlfn.XLOOKUP(
+      <c r="R175" cm="1">
+        <f t="array" ref="R175">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>211</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>457</v>
       </c>
@@ -12618,17 +13165,20 @@
       <c r="N176" t="s">
         <v>21</v>
       </c>
-      <c r="P176">
+      <c r="P176" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q176">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>176</v>
       </c>
-      <c r="Q176" cm="1">
-        <f t="array" ref="Q176">_xlfn.XLOOKUP(
+      <c r="R176" cm="1">
+        <f t="array" ref="R176">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>212</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>457</v>
       </c>
@@ -12668,17 +13218,20 @@
       <c r="N177" t="s">
         <v>5</v>
       </c>
-      <c r="P177">
+      <c r="P177" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q177">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>177</v>
       </c>
-      <c r="Q177" cm="1">
-        <f t="array" ref="Q177">_xlfn.XLOOKUP(
+      <c r="R177" cm="1">
+        <f t="array" ref="R177">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>213</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>457</v>
       </c>
@@ -12718,17 +13271,20 @@
       <c r="N178" t="s">
         <v>5</v>
       </c>
-      <c r="P178">
+      <c r="P178" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q178">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>178</v>
       </c>
-      <c r="Q178" cm="1">
-        <f t="array" ref="Q178">_xlfn.XLOOKUP(
+      <c r="R178" cm="1">
+        <f t="array" ref="R178">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>214</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>457</v>
       </c>
@@ -12768,17 +13324,20 @@
       <c r="N179" t="s">
         <v>21</v>
       </c>
-      <c r="P179">
+      <c r="P179" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q179">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>179</v>
       </c>
-      <c r="Q179" cm="1">
-        <f t="array" ref="Q179">_xlfn.XLOOKUP(
+      <c r="R179" cm="1">
+        <f t="array" ref="R179">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>215</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>457</v>
       </c>
@@ -12818,17 +13377,20 @@
       <c r="N180" t="s">
         <v>21</v>
       </c>
-      <c r="P180">
+      <c r="P180" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q180">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>180</v>
       </c>
-      <c r="Q180" cm="1">
-        <f t="array" ref="Q180">_xlfn.XLOOKUP(
+      <c r="R180" cm="1">
+        <f t="array" ref="R180">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>457</v>
       </c>
@@ -12868,17 +13430,20 @@
       <c r="N181" t="s">
         <v>5</v>
       </c>
-      <c r="P181">
+      <c r="P181" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q181">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>181</v>
       </c>
-      <c r="Q181" cm="1">
-        <f t="array" ref="Q181">_xlfn.XLOOKUP(
+      <c r="R181" cm="1">
+        <f t="array" ref="R181">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>209</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>457</v>
       </c>
@@ -12918,17 +13483,20 @@
       <c r="N182" t="s">
         <v>5</v>
       </c>
-      <c r="P182">
+      <c r="P182" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q182">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>182</v>
       </c>
-      <c r="Q182" cm="1">
-        <f t="array" ref="Q182">_xlfn.XLOOKUP(
+      <c r="R182" cm="1">
+        <f t="array" ref="R182">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>210</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>457</v>
       </c>
@@ -12968,17 +13536,20 @@
       <c r="N183" t="s">
         <v>21</v>
       </c>
-      <c r="P183">
+      <c r="P183" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q183">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>183</v>
       </c>
-      <c r="Q183" cm="1">
-        <f t="array" ref="Q183">_xlfn.XLOOKUP(
+      <c r="R183" cm="1">
+        <f t="array" ref="R183">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>457</v>
       </c>
@@ -13018,17 +13589,20 @@
       <c r="N184" t="s">
         <v>21</v>
       </c>
-      <c r="P184">
+      <c r="P184" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q184">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>184</v>
       </c>
-      <c r="Q184" cm="1">
-        <f t="array" ref="Q184">_xlfn.XLOOKUP(
+      <c r="R184" cm="1">
+        <f t="array" ref="R184">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>212</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>457</v>
       </c>
@@ -13068,17 +13642,20 @@
       <c r="N185" t="s">
         <v>5</v>
       </c>
-      <c r="P185">
+      <c r="P185" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q185">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>185</v>
       </c>
-      <c r="Q185" cm="1">
-        <f t="array" ref="Q185">_xlfn.XLOOKUP(
+      <c r="R185" cm="1">
+        <f t="array" ref="R185">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>457</v>
       </c>
@@ -13118,17 +13695,20 @@
       <c r="N186" t="s">
         <v>5</v>
       </c>
-      <c r="P186">
+      <c r="P186" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q186">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>186</v>
       </c>
-      <c r="Q186" cm="1">
-        <f t="array" ref="Q186">_xlfn.XLOOKUP(
+      <c r="R186" cm="1">
+        <f t="array" ref="R186">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>214</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>457</v>
       </c>
@@ -13168,17 +13748,20 @@
       <c r="N187" t="s">
         <v>21</v>
       </c>
-      <c r="P187">
+      <c r="P187" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q187">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>187</v>
       </c>
-      <c r="Q187" cm="1">
-        <f t="array" ref="Q187">_xlfn.XLOOKUP(
+      <c r="R187" cm="1">
+        <f t="array" ref="R187">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>215</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>457</v>
       </c>
@@ -13218,17 +13801,20 @@
       <c r="N188" t="s">
         <v>21</v>
       </c>
-      <c r="P188">
+      <c r="P188" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q188">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>188</v>
       </c>
-      <c r="Q188" cm="1">
-        <f t="array" ref="Q188">_xlfn.XLOOKUP(
+      <c r="R188" cm="1">
+        <f t="array" ref="R188">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>457</v>
       </c>
@@ -13268,17 +13854,20 @@
       <c r="N189" t="s">
         <v>5</v>
       </c>
-      <c r="P189">
+      <c r="P189" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q189">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>189</v>
       </c>
-      <c r="Q189" cm="1">
-        <f t="array" ref="Q189">_xlfn.XLOOKUP(
+      <c r="R189" cm="1">
+        <f t="array" ref="R189">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>189</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>457</v>
       </c>
@@ -13318,17 +13907,20 @@
       <c r="N190" t="s">
         <v>5</v>
       </c>
-      <c r="P190">
+      <c r="P190" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q190">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>190</v>
       </c>
-      <c r="Q190" cm="1">
-        <f t="array" ref="Q190">_xlfn.XLOOKUP(
+      <c r="R190" cm="1">
+        <f t="array" ref="R190">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>190</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>457</v>
       </c>
@@ -13368,17 +13960,20 @@
       <c r="N191" t="s">
         <v>5</v>
       </c>
-      <c r="P191">
+      <c r="P191" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q191">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>191</v>
       </c>
-      <c r="Q191" cm="1">
-        <f t="array" ref="Q191">_xlfn.XLOOKUP(
+      <c r="R191" cm="1">
+        <f t="array" ref="R191">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>191</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>457</v>
       </c>
@@ -13418,17 +14013,20 @@
       <c r="N192" t="s">
         <v>5</v>
       </c>
-      <c r="P192">
+      <c r="P192" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q192">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>192</v>
       </c>
-      <c r="Q192" cm="1">
-        <f t="array" ref="Q192">_xlfn.XLOOKUP(
+      <c r="R192" cm="1">
+        <f t="array" ref="R192">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>192</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>457</v>
       </c>
@@ -13468,17 +14066,20 @@
       <c r="N193" t="s">
         <v>5</v>
       </c>
-      <c r="P193">
+      <c r="P193" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q193">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>193</v>
       </c>
-      <c r="Q193" cm="1">
-        <f t="array" ref="Q193">_xlfn.XLOOKUP(
+      <c r="R193" cm="1">
+        <f t="array" ref="R193">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>201</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>457</v>
       </c>
@@ -13518,17 +14119,20 @@
       <c r="N194" t="s">
         <v>5</v>
       </c>
-      <c r="P194">
+      <c r="P194" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q194">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>194</v>
       </c>
-      <c r="Q194" cm="1">
-        <f t="array" ref="Q194">_xlfn.XLOOKUP(
+      <c r="R194" cm="1">
+        <f t="array" ref="R194">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>202</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>457</v>
       </c>
@@ -13568,17 +14172,20 @@
       <c r="N195" t="s">
         <v>21</v>
       </c>
-      <c r="P195">
+      <c r="P195" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q195">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>195</v>
       </c>
-      <c r="Q195" cm="1">
-        <f t="array" ref="Q195">_xlfn.XLOOKUP(
+      <c r="R195" cm="1">
+        <f t="array" ref="R195">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>203</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>457</v>
       </c>
@@ -13618,17 +14225,20 @@
       <c r="N196" t="s">
         <v>21</v>
       </c>
-      <c r="P196">
+      <c r="P196" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q196">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>196</v>
       </c>
-      <c r="Q196" cm="1">
-        <f t="array" ref="Q196">_xlfn.XLOOKUP(
+      <c r="R196" cm="1">
+        <f t="array" ref="R196">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>204</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>457</v>
       </c>
@@ -13668,17 +14278,20 @@
       <c r="N197" t="s">
         <v>5</v>
       </c>
-      <c r="P197">
+      <c r="P197" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q197">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>197</v>
       </c>
-      <c r="Q197" cm="1">
-        <f t="array" ref="Q197">_xlfn.XLOOKUP(
+      <c r="R197" cm="1">
+        <f t="array" ref="R197">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>205</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>457</v>
       </c>
@@ -13718,17 +14331,20 @@
       <c r="N198" t="s">
         <v>5</v>
       </c>
-      <c r="P198">
+      <c r="P198" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q198">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>198</v>
       </c>
-      <c r="Q198" cm="1">
-        <f t="array" ref="Q198">_xlfn.XLOOKUP(
+      <c r="R198" cm="1">
+        <f t="array" ref="R198">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>206</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>457</v>
       </c>
@@ -13768,17 +14384,20 @@
       <c r="N199" t="s">
         <v>21</v>
       </c>
-      <c r="P199">
+      <c r="P199" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q199">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>199</v>
       </c>
-      <c r="Q199" cm="1">
-        <f t="array" ref="Q199">_xlfn.XLOOKUP(
+      <c r="R199" cm="1">
+        <f t="array" ref="R199">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>207</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>457</v>
       </c>
@@ -13818,17 +14437,20 @@
       <c r="N200" t="s">
         <v>21</v>
       </c>
-      <c r="P200">
+      <c r="P200" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q200">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>200</v>
       </c>
-      <c r="Q200" cm="1">
-        <f t="array" ref="Q200">_xlfn.XLOOKUP(
+      <c r="R200" cm="1">
+        <f t="array" ref="R200">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>208</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>457</v>
       </c>
@@ -13868,17 +14490,20 @@
       <c r="N201" t="s">
         <v>5</v>
       </c>
-      <c r="P201">
+      <c r="P201" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q201">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>201</v>
       </c>
-      <c r="Q201" cm="1">
-        <f t="array" ref="Q201">_xlfn.XLOOKUP(
+      <c r="R201" cm="1">
+        <f t="array" ref="R201">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>201</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>457</v>
       </c>
@@ -13918,17 +14543,20 @@
       <c r="N202" t="s">
         <v>5</v>
       </c>
-      <c r="P202">
+      <c r="P202" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q202">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>202</v>
       </c>
-      <c r="Q202" cm="1">
-        <f t="array" ref="Q202">_xlfn.XLOOKUP(
+      <c r="R202" cm="1">
+        <f t="array" ref="R202">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>202</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>457</v>
       </c>
@@ -13968,17 +14596,20 @@
       <c r="N203" t="s">
         <v>21</v>
       </c>
-      <c r="P203">
+      <c r="P203" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q203">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>203</v>
       </c>
-      <c r="Q203" cm="1">
-        <f t="array" ref="Q203">_xlfn.XLOOKUP(
+      <c r="R203" cm="1">
+        <f t="array" ref="R203">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>203</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>457</v>
       </c>
@@ -14018,17 +14649,20 @@
       <c r="N204" t="s">
         <v>21</v>
       </c>
-      <c r="P204">
+      <c r="P204" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q204">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>204</v>
       </c>
-      <c r="Q204" cm="1">
-        <f t="array" ref="Q204">_xlfn.XLOOKUP(
+      <c r="R204" cm="1">
+        <f t="array" ref="R204">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>457</v>
       </c>
@@ -14068,17 +14702,20 @@
       <c r="N205" t="s">
         <v>5</v>
       </c>
-      <c r="P205">
+      <c r="P205" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q205">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>205</v>
       </c>
-      <c r="Q205" cm="1">
-        <f t="array" ref="Q205">_xlfn.XLOOKUP(
+      <c r="R205" cm="1">
+        <f t="array" ref="R205">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>205</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>457</v>
       </c>
@@ -14118,17 +14755,20 @@
       <c r="N206" t="s">
         <v>5</v>
       </c>
-      <c r="P206">
+      <c r="P206" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q206">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>206</v>
       </c>
-      <c r="Q206" cm="1">
-        <f t="array" ref="Q206">_xlfn.XLOOKUP(
+      <c r="R206" cm="1">
+        <f t="array" ref="R206">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>206</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>457</v>
       </c>
@@ -14168,17 +14808,20 @@
       <c r="N207" t="s">
         <v>21</v>
       </c>
-      <c r="P207">
+      <c r="P207" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q207">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>207</v>
       </c>
-      <c r="Q207" cm="1">
-        <f t="array" ref="Q207">_xlfn.XLOOKUP(
+      <c r="R207" cm="1">
+        <f t="array" ref="R207">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>207</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>457</v>
       </c>
@@ -14218,17 +14861,20 @@
       <c r="N208" t="s">
         <v>21</v>
       </c>
-      <c r="P208">
+      <c r="P208" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q208">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>208</v>
       </c>
-      <c r="Q208" cm="1">
-        <f t="array" ref="Q208">_xlfn.XLOOKUP(
+      <c r="R208" cm="1">
+        <f t="array" ref="R208">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>208</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>457</v>
       </c>
@@ -14268,17 +14914,20 @@
       <c r="N209" t="s">
         <v>5</v>
       </c>
-      <c r="P209">
+      <c r="P209" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q209">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>209</v>
       </c>
-      <c r="Q209" cm="1">
-        <f t="array" ref="Q209">_xlfn.XLOOKUP(
+      <c r="R209" cm="1">
+        <f t="array" ref="R209">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>209</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>457</v>
       </c>
@@ -14318,17 +14967,20 @@
       <c r="N210" t="s">
         <v>5</v>
       </c>
-      <c r="P210">
+      <c r="P210" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q210">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>210</v>
       </c>
-      <c r="Q210" cm="1">
-        <f t="array" ref="Q210">_xlfn.XLOOKUP(
+      <c r="R210" cm="1">
+        <f t="array" ref="R210">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>210</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>457</v>
       </c>
@@ -14368,17 +15020,20 @@
       <c r="N211" t="s">
         <v>21</v>
       </c>
-      <c r="P211">
+      <c r="P211" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q211">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>211</v>
       </c>
-      <c r="Q211" cm="1">
-        <f t="array" ref="Q211">_xlfn.XLOOKUP(
+      <c r="R211" cm="1">
+        <f t="array" ref="R211">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>211</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>457</v>
       </c>
@@ -14418,17 +15073,20 @@
       <c r="N212" t="s">
         <v>21</v>
       </c>
-      <c r="P212">
+      <c r="P212" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q212">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>212</v>
       </c>
-      <c r="Q212" cm="1">
-        <f t="array" ref="Q212">_xlfn.XLOOKUP(
+      <c r="R212" cm="1">
+        <f t="array" ref="R212">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>212</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>457</v>
       </c>
@@ -14468,17 +15126,20 @@
       <c r="N213" t="s">
         <v>5</v>
       </c>
-      <c r="P213">
+      <c r="P213" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q213">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>213</v>
       </c>
-      <c r="Q213" cm="1">
-        <f t="array" ref="Q213">_xlfn.XLOOKUP(
+      <c r="R213" cm="1">
+        <f t="array" ref="R213">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>213</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>457</v>
       </c>
@@ -14518,17 +15179,20 @@
       <c r="N214" t="s">
         <v>5</v>
       </c>
-      <c r="P214">
+      <c r="P214" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q214">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>214</v>
       </c>
-      <c r="Q214" cm="1">
-        <f t="array" ref="Q214">_xlfn.XLOOKUP(
+      <c r="R214" cm="1">
+        <f t="array" ref="R214">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>214</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>457</v>
       </c>
@@ -14568,17 +15232,20 @@
       <c r="N215" t="s">
         <v>21</v>
       </c>
-      <c r="P215">
+      <c r="P215" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q215">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>215</v>
       </c>
-      <c r="Q215" cm="1">
-        <f t="array" ref="Q215">_xlfn.XLOOKUP(
+      <c r="R215" cm="1">
+        <f t="array" ref="R215">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>215</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>457</v>
       </c>
@@ -14618,17 +15285,20 @@
       <c r="N216" t="s">
         <v>21</v>
       </c>
-      <c r="P216">
+      <c r="P216" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q216">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>216</v>
       </c>
-      <c r="Q216" cm="1">
-        <f t="array" ref="Q216">_xlfn.XLOOKUP(
+      <c r="R216" cm="1">
+        <f t="array" ref="R216">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>457</v>
       </c>
@@ -14668,17 +15338,20 @@
       <c r="N217" t="s">
         <v>5</v>
       </c>
-      <c r="P217">
+      <c r="P217" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q217">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>217</v>
       </c>
-      <c r="Q217" cm="1">
-        <f t="array" ref="Q217">_xlfn.XLOOKUP(
+      <c r="R217" cm="1">
+        <f t="array" ref="R217">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>225</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>457</v>
       </c>
@@ -14718,17 +15391,20 @@
       <c r="N218" t="s">
         <v>5</v>
       </c>
-      <c r="P218">
+      <c r="P218" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q218">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>218</v>
       </c>
-      <c r="Q218" cm="1">
-        <f t="array" ref="Q218">_xlfn.XLOOKUP(
+      <c r="R218" cm="1">
+        <f t="array" ref="R218">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>226</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>457</v>
       </c>
@@ -14768,17 +15444,20 @@
       <c r="N219" t="s">
         <v>21</v>
       </c>
-      <c r="P219">
+      <c r="P219" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q219">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>219</v>
       </c>
-      <c r="Q219" cm="1">
-        <f t="array" ref="Q219">_xlfn.XLOOKUP(
+      <c r="R219" cm="1">
+        <f t="array" ref="R219">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>227</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>457</v>
       </c>
@@ -14818,17 +15497,20 @@
       <c r="N220" t="s">
         <v>21</v>
       </c>
-      <c r="P220">
+      <c r="P220" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q220">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>220</v>
       </c>
-      <c r="Q220" cm="1">
-        <f t="array" ref="Q220">_xlfn.XLOOKUP(
+      <c r="R220" cm="1">
+        <f t="array" ref="R220">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>228</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>457</v>
       </c>
@@ -14868,17 +15550,20 @@
       <c r="N221" t="s">
         <v>5</v>
       </c>
-      <c r="P221">
+      <c r="P221" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q221">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>221</v>
       </c>
-      <c r="Q221" cm="1">
-        <f t="array" ref="Q221">_xlfn.XLOOKUP(
+      <c r="R221" cm="1">
+        <f t="array" ref="R221">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>229</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>457</v>
       </c>
@@ -14918,17 +15603,20 @@
       <c r="N222" t="s">
         <v>5</v>
       </c>
-      <c r="P222">
+      <c r="P222" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q222">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>222</v>
       </c>
-      <c r="Q222" cm="1">
-        <f t="array" ref="Q222">_xlfn.XLOOKUP(
+      <c r="R222" cm="1">
+        <f t="array" ref="R222">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>230</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>457</v>
       </c>
@@ -14968,17 +15656,20 @@
       <c r="N223" t="s">
         <v>21</v>
       </c>
-      <c r="P223">
+      <c r="P223" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q223">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>223</v>
       </c>
-      <c r="Q223" cm="1">
-        <f t="array" ref="Q223">_xlfn.XLOOKUP(
+      <c r="R223" cm="1">
+        <f t="array" ref="R223">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>231</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>457</v>
       </c>
@@ -15018,17 +15709,20 @@
       <c r="N224" t="s">
         <v>21</v>
       </c>
-      <c r="P224">
+      <c r="P224" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q224">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>224</v>
       </c>
-      <c r="Q224" cm="1">
-        <f t="array" ref="Q224">_xlfn.XLOOKUP(
+      <c r="R224" cm="1">
+        <f t="array" ref="R224">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>232</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>457</v>
       </c>
@@ -15068,17 +15762,20 @@
       <c r="N225" t="s">
         <v>5</v>
       </c>
-      <c r="P225">
+      <c r="P225" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q225">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>225</v>
       </c>
-      <c r="Q225" cm="1">
-        <f t="array" ref="Q225">_xlfn.XLOOKUP(
+      <c r="R225" cm="1">
+        <f t="array" ref="R225">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>225</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>457</v>
       </c>
@@ -15118,17 +15815,20 @@
       <c r="N226" t="s">
         <v>5</v>
       </c>
-      <c r="P226">
+      <c r="P226" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q226">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>226</v>
       </c>
-      <c r="Q226" cm="1">
-        <f t="array" ref="Q226">_xlfn.XLOOKUP(
+      <c r="R226" cm="1">
+        <f t="array" ref="R226">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>226</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>457</v>
       </c>
@@ -15168,17 +15868,20 @@
       <c r="N227" t="s">
         <v>21</v>
       </c>
-      <c r="P227">
+      <c r="P227" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q227">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>227</v>
       </c>
-      <c r="Q227" cm="1">
-        <f t="array" ref="Q227">_xlfn.XLOOKUP(
+      <c r="R227" cm="1">
+        <f t="array" ref="R227">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>227</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>457</v>
       </c>
@@ -15218,17 +15921,20 @@
       <c r="N228" t="s">
         <v>21</v>
       </c>
-      <c r="P228">
+      <c r="P228" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q228">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>228</v>
       </c>
-      <c r="Q228" cm="1">
-        <f t="array" ref="Q228">_xlfn.XLOOKUP(
+      <c r="R228" cm="1">
+        <f t="array" ref="R228">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>228</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>457</v>
       </c>
@@ -15268,17 +15974,20 @@
       <c r="N229" t="s">
         <v>5</v>
       </c>
-      <c r="P229">
+      <c r="P229" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q229">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>229</v>
       </c>
-      <c r="Q229" cm="1">
-        <f t="array" ref="Q229">_xlfn.XLOOKUP(
+      <c r="R229" cm="1">
+        <f t="array" ref="R229">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>229</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>457</v>
       </c>
@@ -15318,17 +16027,20 @@
       <c r="N230" t="s">
         <v>5</v>
       </c>
-      <c r="P230">
+      <c r="P230" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q230">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>230</v>
       </c>
-      <c r="Q230" cm="1">
-        <f t="array" ref="Q230">_xlfn.XLOOKUP(
+      <c r="R230" cm="1">
+        <f t="array" ref="R230">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>230</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>457</v>
       </c>
@@ -15368,17 +16080,20 @@
       <c r="N231" t="s">
         <v>21</v>
       </c>
-      <c r="P231">
+      <c r="P231" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q231">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>231</v>
       </c>
-      <c r="Q231" cm="1">
-        <f t="array" ref="Q231">_xlfn.XLOOKUP(
+      <c r="R231" cm="1">
+        <f t="array" ref="R231">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>231</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>457</v>
       </c>
@@ -15418,17 +16133,20 @@
       <c r="N232" t="s">
         <v>21</v>
       </c>
-      <c r="P232">
+      <c r="P232" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q232">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>232</v>
       </c>
-      <c r="Q232" cm="1">
-        <f t="array" ref="Q232">_xlfn.XLOOKUP(
+      <c r="R232" cm="1">
+        <f t="array" ref="R232">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>232</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>669</v>
       </c>
@@ -15468,17 +16186,20 @@
       <c r="N233" t="s">
         <v>5</v>
       </c>
-      <c r="P233">
+      <c r="P233" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q233">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>233</v>
       </c>
-      <c r="Q233" cm="1">
-        <f t="array" ref="Q233">_xlfn.XLOOKUP(
+      <c r="R233" cm="1">
+        <f t="array" ref="R233">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>233</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>669</v>
       </c>
@@ -15518,17 +16239,20 @@
       <c r="N234" t="s">
         <v>5</v>
       </c>
-      <c r="P234">
+      <c r="P234" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q234">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>234</v>
       </c>
-      <c r="Q234" cm="1">
-        <f t="array" ref="Q234">_xlfn.XLOOKUP(
+      <c r="R234" cm="1">
+        <f t="array" ref="R234">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>234</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>669</v>
       </c>
@@ -15568,17 +16292,20 @@
       <c r="N235" t="s">
         <v>5</v>
       </c>
-      <c r="P235">
+      <c r="P235" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q235">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>235</v>
       </c>
-      <c r="Q235" cm="1">
-        <f t="array" ref="Q235">_xlfn.XLOOKUP(
+      <c r="R235" cm="1">
+        <f t="array" ref="R235">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>235</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>669</v>
       </c>
@@ -15618,17 +16345,20 @@
       <c r="N236" t="s">
         <v>5</v>
       </c>
-      <c r="P236">
+      <c r="P236" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q236">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>236</v>
       </c>
-      <c r="Q236" cm="1">
-        <f t="array" ref="Q236">_xlfn.XLOOKUP(
+      <c r="R236" cm="1">
+        <f t="array" ref="R236">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>236</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>669</v>
       </c>
@@ -15668,17 +16398,20 @@
       <c r="N237" t="s">
         <v>5</v>
       </c>
-      <c r="P237">
+      <c r="P237" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q237">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>237</v>
       </c>
-      <c r="Q237" cm="1">
-        <f t="array" ref="Q237">_xlfn.XLOOKUP(
+      <c r="R237" cm="1">
+        <f t="array" ref="R237">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>237</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>669</v>
       </c>
@@ -15718,17 +16451,20 @@
       <c r="N238" t="s">
         <v>5</v>
       </c>
-      <c r="P238">
+      <c r="P238" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q238">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>238</v>
       </c>
-      <c r="Q238" cm="1">
-        <f t="array" ref="Q238">_xlfn.XLOOKUP(
+      <c r="R238" cm="1">
+        <f t="array" ref="R238">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>238</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>669</v>
       </c>
@@ -15768,17 +16504,20 @@
       <c r="N239" t="s">
         <v>21</v>
       </c>
-      <c r="P239">
+      <c r="P239" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q239">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>239</v>
       </c>
-      <c r="Q239" cm="1">
-        <f t="array" ref="Q239">_xlfn.XLOOKUP(
+      <c r="R239" cm="1">
+        <f t="array" ref="R239">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>239</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>685</v>
       </c>
@@ -15818,17 +16557,20 @@
       <c r="N240" t="s">
         <v>194</v>
       </c>
-      <c r="P240">
+      <c r="P240" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q240">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>240</v>
       </c>
-      <c r="Q240" cm="1">
-        <f t="array" ref="Q240">_xlfn.XLOOKUP(
+      <c r="R240" cm="1">
+        <f t="array" ref="R240">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>685</v>
       </c>
@@ -15868,17 +16610,20 @@
       <c r="N241" t="s">
         <v>194</v>
       </c>
-      <c r="P241">
+      <c r="P241" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q241">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>241</v>
       </c>
-      <c r="Q241" cm="1">
-        <f t="array" ref="Q241">_xlfn.XLOOKUP(
+      <c r="R241" cm="1">
+        <f t="array" ref="R241">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>241</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>685</v>
       </c>
@@ -15918,17 +16663,20 @@
       <c r="N242" t="s">
         <v>194</v>
       </c>
-      <c r="P242">
+      <c r="P242" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q242">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>242</v>
       </c>
-      <c r="Q242" cm="1">
-        <f t="array" ref="Q242">_xlfn.XLOOKUP(
+      <c r="R242" cm="1">
+        <f t="array" ref="R242">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>242</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>685</v>
       </c>
@@ -15968,17 +16716,20 @@
       <c r="N243" t="s">
         <v>194</v>
       </c>
-      <c r="P243">
+      <c r="P243" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q243">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>243</v>
       </c>
-      <c r="Q243" cm="1">
-        <f t="array" ref="Q243">_xlfn.XLOOKUP(
+      <c r="R243" cm="1">
+        <f t="array" ref="R243">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>243</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>685</v>
       </c>
@@ -16018,17 +16769,20 @@
       <c r="N244" t="s">
         <v>5</v>
       </c>
-      <c r="P244">
+      <c r="P244" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q244">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>244</v>
       </c>
-      <c r="Q244" cm="1">
-        <f t="array" ref="Q244">_xlfn.XLOOKUP(
+      <c r="R244" cm="1">
+        <f t="array" ref="R244">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>244</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>685</v>
       </c>
@@ -16068,17 +16822,20 @@
       <c r="N245" t="s">
         <v>5</v>
       </c>
-      <c r="P245">
+      <c r="P245" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q245">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>245</v>
       </c>
-      <c r="Q245" cm="1">
-        <f t="array" ref="Q245">_xlfn.XLOOKUP(
+      <c r="R245" cm="1">
+        <f t="array" ref="R245">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>245</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>685</v>
       </c>
@@ -16118,17 +16875,20 @@
       <c r="N246" t="s">
         <v>5</v>
       </c>
-      <c r="P246">
+      <c r="P246" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q246">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>246</v>
       </c>
-      <c r="Q246" cm="1">
-        <f t="array" ref="Q246">_xlfn.XLOOKUP(
+      <c r="R246" cm="1">
+        <f t="array" ref="R246">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>246</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>685</v>
       </c>
@@ -16168,17 +16928,20 @@
       <c r="N247" t="s">
         <v>5</v>
       </c>
-      <c r="P247">
+      <c r="P247" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q247">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>247</v>
       </c>
-      <c r="Q247" cm="1">
-        <f t="array" ref="Q247">_xlfn.XLOOKUP(
+      <c r="R247" cm="1">
+        <f t="array" ref="R247">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>247</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>685</v>
       </c>
@@ -16218,17 +16981,20 @@
       <c r="N248" t="s">
         <v>5</v>
       </c>
-      <c r="P248">
+      <c r="P248" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q248">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>248</v>
       </c>
-      <c r="Q248" cm="1">
-        <f t="array" ref="Q248">_xlfn.XLOOKUP(
+      <c r="R248" cm="1">
+        <f t="array" ref="R248">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>248</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>685</v>
       </c>
@@ -16268,17 +17034,20 @@
       <c r="N249" t="s">
         <v>5</v>
       </c>
-      <c r="P249">
+      <c r="P249" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q249">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>249</v>
       </c>
-      <c r="Q249" cm="1">
-        <f t="array" ref="Q249">_xlfn.XLOOKUP(
+      <c r="R249" cm="1">
+        <f t="array" ref="R249">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>249</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>685</v>
       </c>
@@ -16318,17 +17087,20 @@
       <c r="N250" t="s">
         <v>5</v>
       </c>
-      <c r="P250">
+      <c r="P250" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q250">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>250</v>
       </c>
-      <c r="Q250" cm="1">
-        <f t="array" ref="Q250">_xlfn.XLOOKUP(
+      <c r="R250" cm="1">
+        <f t="array" ref="R250">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>250</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>685</v>
       </c>
@@ -16368,17 +17140,20 @@
       <c r="N251" t="s">
         <v>5</v>
       </c>
-      <c r="P251">
+      <c r="P251" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q251">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>251</v>
       </c>
-      <c r="Q251" cm="1">
-        <f t="array" ref="Q251">_xlfn.XLOOKUP(
+      <c r="R251" cm="1">
+        <f t="array" ref="R251">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>251</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>685</v>
       </c>
@@ -16418,17 +17193,20 @@
       <c r="N252" t="s">
         <v>5</v>
       </c>
-      <c r="P252">
+      <c r="P252" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q252">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>252</v>
       </c>
-      <c r="Q252" cm="1">
-        <f t="array" ref="Q252">_xlfn.XLOOKUP(
+      <c r="R252" cm="1">
+        <f t="array" ref="R252">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>252</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>720</v>
       </c>
@@ -16468,17 +17246,20 @@
       <c r="N253" t="s">
         <v>5</v>
       </c>
-      <c r="P253">
+      <c r="P253" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q253">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>253</v>
       </c>
-      <c r="Q253" cm="1">
-        <f t="array" ref="Q253">_xlfn.XLOOKUP(
+      <c r="R253" cm="1">
+        <f t="array" ref="R253">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>253</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>720</v>
       </c>
@@ -16518,17 +17299,20 @@
       <c r="N254" t="s">
         <v>5</v>
       </c>
-      <c r="P254">
+      <c r="P254" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q254">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>254</v>
       </c>
-      <c r="Q254" cm="1">
-        <f t="array" ref="Q254">_xlfn.XLOOKUP(
+      <c r="R254" cm="1">
+        <f t="array" ref="R254">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>254</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>720</v>
       </c>
@@ -16568,17 +17352,20 @@
       <c r="N255" t="s">
         <v>5</v>
       </c>
-      <c r="P255">
+      <c r="P255" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q255">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>255</v>
       </c>
-      <c r="Q255" cm="1">
-        <f t="array" ref="Q255">_xlfn.XLOOKUP(
+      <c r="R255" cm="1">
+        <f t="array" ref="R255">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>255</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>720</v>
       </c>
@@ -16618,17 +17405,20 @@
       <c r="N256" t="s">
         <v>5</v>
       </c>
-      <c r="P256">
+      <c r="P256" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q256">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>256</v>
       </c>
-      <c r="Q256" cm="1">
-        <f t="array" ref="Q256">_xlfn.XLOOKUP(
+      <c r="R256" cm="1">
+        <f t="array" ref="R256">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>256</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>720</v>
       </c>
@@ -16668,17 +17458,20 @@
       <c r="N257" t="s">
         <v>194</v>
       </c>
-      <c r="P257">
+      <c r="P257" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q257">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>257</v>
       </c>
-      <c r="Q257" cm="1">
-        <f t="array" ref="Q257">_xlfn.XLOOKUP(
+      <c r="R257" cm="1">
+        <f t="array" ref="R257">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>257</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>720</v>
       </c>
@@ -16718,17 +17511,20 @@
       <c r="N258" t="s">
         <v>194</v>
       </c>
-      <c r="P258">
+      <c r="P258" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q258">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>258</v>
       </c>
-      <c r="Q258" cm="1">
-        <f t="array" ref="Q258">_xlfn.XLOOKUP(
+      <c r="R258" cm="1">
+        <f t="array" ref="R258">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>258</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>720</v>
       </c>
@@ -16768,17 +17564,20 @@
       <c r="N259" t="s">
         <v>194</v>
       </c>
-      <c r="P259">
+      <c r="P259" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q259">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>259</v>
       </c>
-      <c r="Q259" cm="1">
-        <f t="array" ref="Q259">_xlfn.XLOOKUP(
+      <c r="R259" cm="1">
+        <f t="array" ref="R259">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>259</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>720</v>
       </c>
@@ -16818,17 +17617,20 @@
       <c r="N260" t="s">
         <v>194</v>
       </c>
-      <c r="P260">
+      <c r="P260" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q260">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>260</v>
       </c>
-      <c r="Q260" cm="1">
-        <f t="array" ref="Q260">_xlfn.XLOOKUP(
+      <c r="R260" cm="1">
+        <f t="array" ref="R260">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>260</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>720</v>
       </c>
@@ -16868,17 +17670,20 @@
       <c r="N261" t="s">
         <v>5</v>
       </c>
-      <c r="P261">
+      <c r="P261" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q261">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>261</v>
       </c>
-      <c r="Q261" cm="1">
-        <f t="array" ref="Q261">_xlfn.XLOOKUP(
+      <c r="R261" cm="1">
+        <f t="array" ref="R261">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>261</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>720</v>
       </c>
@@ -16918,17 +17723,20 @@
       <c r="N262" t="s">
         <v>5</v>
       </c>
-      <c r="P262">
+      <c r="P262" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q262">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>262</v>
       </c>
-      <c r="Q262" cm="1">
-        <f t="array" ref="Q262">_xlfn.XLOOKUP(
+      <c r="R262" cm="1">
+        <f t="array" ref="R262">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>262</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>720</v>
       </c>
@@ -16968,17 +17776,20 @@
       <c r="N263" t="s">
         <v>194</v>
       </c>
-      <c r="P263">
+      <c r="P263" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q263">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>263</v>
       </c>
-      <c r="Q263" cm="1">
-        <f t="array" ref="Q263">_xlfn.XLOOKUP(
+      <c r="R263" cm="1">
+        <f t="array" ref="R263">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>263</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>720</v>
       </c>
@@ -17018,17 +17829,20 @@
       <c r="N264" t="s">
         <v>194</v>
       </c>
-      <c r="P264">
+      <c r="P264" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q264">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>264</v>
       </c>
-      <c r="Q264" cm="1">
-        <f t="array" ref="Q264">_xlfn.XLOOKUP(
+      <c r="R264" cm="1">
+        <f t="array" ref="R264">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>264</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>720</v>
       </c>
@@ -17068,17 +17882,20 @@
       <c r="N265" t="s">
         <v>194</v>
       </c>
-      <c r="P265">
+      <c r="P265" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q265">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>265</v>
       </c>
-      <c r="Q265" cm="1">
-        <f t="array" ref="Q265">_xlfn.XLOOKUP(
+      <c r="R265" cm="1">
+        <f t="array" ref="R265">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>265</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>720</v>
       </c>
@@ -17118,17 +17935,20 @@
       <c r="N266" t="s">
         <v>194</v>
       </c>
-      <c r="P266">
+      <c r="P266" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q266">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>266</v>
       </c>
-      <c r="Q266" cm="1">
-        <f t="array" ref="Q266">_xlfn.XLOOKUP(
+      <c r="R266" cm="1">
+        <f t="array" ref="R266">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>266</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>720</v>
       </c>
@@ -17168,17 +17988,20 @@
       <c r="N267" t="s">
         <v>5</v>
       </c>
-      <c r="P267">
+      <c r="P267" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q267">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>267</v>
       </c>
-      <c r="Q267" cm="1">
-        <f t="array" ref="Q267">_xlfn.XLOOKUP(
+      <c r="R267" cm="1">
+        <f t="array" ref="R267">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>267</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>720</v>
       </c>
@@ -17218,17 +18041,20 @@
       <c r="N268" t="s">
         <v>5</v>
       </c>
-      <c r="P268">
+      <c r="P268" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q268">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>268</v>
       </c>
-      <c r="Q268" cm="1">
-        <f t="array" ref="Q268">_xlfn.XLOOKUP(
+      <c r="R268" cm="1">
+        <f t="array" ref="R268">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>268</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>720</v>
       </c>
@@ -17268,17 +18094,20 @@
       <c r="N269" t="s">
         <v>194</v>
       </c>
-      <c r="P269">
+      <c r="P269" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q269">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>269</v>
       </c>
-      <c r="Q269" cm="1">
-        <f t="array" ref="Q269">_xlfn.XLOOKUP(
+      <c r="R269" cm="1">
+        <f t="array" ref="R269">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>269</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>720</v>
       </c>
@@ -17318,17 +18147,20 @@
       <c r="N270" t="s">
         <v>194</v>
       </c>
-      <c r="P270">
+      <c r="P270" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q270">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>270</v>
       </c>
-      <c r="Q270" cm="1">
-        <f t="array" ref="Q270">_xlfn.XLOOKUP(
+      <c r="R270" cm="1">
+        <f t="array" ref="R270">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>270</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>720</v>
       </c>
@@ -17368,17 +18200,20 @@
       <c r="N271" t="s">
         <v>194</v>
       </c>
-      <c r="P271">
+      <c r="P271" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q271">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>271</v>
       </c>
-      <c r="Q271" cm="1">
-        <f t="array" ref="Q271">_xlfn.XLOOKUP(
+      <c r="R271" cm="1">
+        <f t="array" ref="R271">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>271</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>720</v>
       </c>
@@ -17418,17 +18253,20 @@
       <c r="N272" t="s">
         <v>194</v>
       </c>
-      <c r="P272">
+      <c r="P272" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q272">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>272</v>
       </c>
-      <c r="Q272" cm="1">
-        <f t="array" ref="Q272">_xlfn.XLOOKUP(
+      <c r="R272" cm="1">
+        <f t="array" ref="R272">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>272</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>720</v>
       </c>
@@ -17468,17 +18306,20 @@
       <c r="N273" t="s">
         <v>5</v>
       </c>
-      <c r="P273">
+      <c r="P273" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q273">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>273</v>
       </c>
-      <c r="Q273" cm="1">
-        <f t="array" ref="Q273">_xlfn.XLOOKUP(
+      <c r="R273" cm="1">
+        <f t="array" ref="R273">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>273</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>720</v>
       </c>
@@ -17518,17 +18359,20 @@
       <c r="N274" t="s">
         <v>5</v>
       </c>
-      <c r="P274">
+      <c r="P274" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q274">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>274</v>
       </c>
-      <c r="Q274" cm="1">
-        <f t="array" ref="Q274">_xlfn.XLOOKUP(
+      <c r="R274" cm="1">
+        <f t="array" ref="R274">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>274</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>779</v>
       </c>
@@ -17568,17 +18412,20 @@
       <c r="N275" t="s">
         <v>194</v>
       </c>
-      <c r="P275">
+      <c r="P275" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q275">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>275</v>
       </c>
-      <c r="Q275" cm="1">
-        <f t="array" ref="Q275">_xlfn.XLOOKUP(
+      <c r="R275" cm="1">
+        <f t="array" ref="R275">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>275</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>779</v>
       </c>
@@ -17618,17 +18465,20 @@
       <c r="N276" t="s">
         <v>194</v>
       </c>
-      <c r="P276">
+      <c r="P276" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q276">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>276</v>
       </c>
-      <c r="Q276" cm="1">
-        <f t="array" ref="Q276">_xlfn.XLOOKUP(
+      <c r="R276" cm="1">
+        <f t="array" ref="R276">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>276</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>779</v>
       </c>
@@ -17668,17 +18518,20 @@
       <c r="N277" t="s">
         <v>5</v>
       </c>
-      <c r="P277">
+      <c r="P277" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q277">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>277</v>
       </c>
-      <c r="Q277" cm="1">
-        <f t="array" ref="Q277">_xlfn.XLOOKUP(
+      <c r="R277" cm="1">
+        <f t="array" ref="R277">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>277</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>779</v>
       </c>
@@ -17718,17 +18571,20 @@
       <c r="N278" t="s">
         <v>5</v>
       </c>
-      <c r="P278">
+      <c r="P278" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q278">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>278</v>
       </c>
-      <c r="Q278" cm="1">
-        <f t="array" ref="Q278">_xlfn.XLOOKUP(
+      <c r="R278" cm="1">
+        <f t="array" ref="R278">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>278</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>779</v>
       </c>
@@ -17768,17 +18624,20 @@
       <c r="N279" t="s">
         <v>5</v>
       </c>
-      <c r="P279">
+      <c r="P279" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q279">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>279</v>
       </c>
-      <c r="Q279" cm="1">
-        <f t="array" ref="Q279">_xlfn.XLOOKUP(
+      <c r="R279" cm="1">
+        <f t="array" ref="R279">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>279</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>779</v>
       </c>
@@ -17818,17 +18677,20 @@
       <c r="N280" t="s">
         <v>194</v>
       </c>
-      <c r="P280">
+      <c r="P280" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q280">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>280</v>
       </c>
-      <c r="Q280" cm="1">
-        <f t="array" ref="Q280">_xlfn.XLOOKUP(
+      <c r="R280" cm="1">
+        <f t="array" ref="R280">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>280</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>779</v>
       </c>
@@ -17868,17 +18730,20 @@
       <c r="N281" t="s">
         <v>194</v>
       </c>
-      <c r="P281">
+      <c r="P281" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q281">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>281</v>
       </c>
-      <c r="Q281" cm="1">
-        <f t="array" ref="Q281">_xlfn.XLOOKUP(
+      <c r="R281" cm="1">
+        <f t="array" ref="R281">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>281</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>779</v>
       </c>
@@ -17918,17 +18783,20 @@
       <c r="N282" t="s">
         <v>194</v>
       </c>
-      <c r="P282">
+      <c r="P282" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q282">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>282</v>
       </c>
-      <c r="Q282" cm="1">
-        <f t="array" ref="Q282">_xlfn.XLOOKUP(
+      <c r="R282" cm="1">
+        <f t="array" ref="R282">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>282</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>779</v>
       </c>
@@ -17968,17 +18836,20 @@
       <c r="N283" t="s">
         <v>194</v>
       </c>
-      <c r="P283">
+      <c r="P283" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q283">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>283</v>
       </c>
-      <c r="Q283" cm="1">
-        <f t="array" ref="Q283">_xlfn.XLOOKUP(
+      <c r="R283" cm="1">
+        <f t="array" ref="R283">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>283</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>779</v>
       </c>
@@ -18018,17 +18889,20 @@
       <c r="N284" t="s">
         <v>194</v>
       </c>
-      <c r="P284">
+      <c r="P284" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q284">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>284</v>
       </c>
-      <c r="Q284" cm="1">
-        <f t="array" ref="Q284">_xlfn.XLOOKUP(
+      <c r="R284" cm="1">
+        <f t="array" ref="R284">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>284</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>779</v>
       </c>
@@ -18068,17 +18942,20 @@
       <c r="N285" t="s">
         <v>194</v>
       </c>
-      <c r="P285">
+      <c r="P285" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q285">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>285</v>
       </c>
-      <c r="Q285" cm="1">
-        <f t="array" ref="Q285">_xlfn.XLOOKUP(
+      <c r="R285" cm="1">
+        <f t="array" ref="R285">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>779</v>
       </c>
@@ -18118,17 +18995,20 @@
       <c r="N286" t="s">
         <v>5</v>
       </c>
-      <c r="P286">
+      <c r="P286" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q286">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>286</v>
       </c>
-      <c r="Q286" cm="1">
-        <f t="array" ref="Q286">_xlfn.XLOOKUP(
+      <c r="R286" cm="1">
+        <f t="array" ref="R286">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>286</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>779</v>
       </c>
@@ -18168,17 +19048,20 @@
       <c r="N287" t="s">
         <v>5</v>
       </c>
-      <c r="P287">
+      <c r="P287" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q287">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>287</v>
       </c>
-      <c r="Q287" cm="1">
-        <f t="array" ref="Q287">_xlfn.XLOOKUP(
+      <c r="R287" cm="1">
+        <f t="array" ref="R287">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>287</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>779</v>
       </c>
@@ -18218,17 +19101,20 @@
       <c r="N288" t="s">
         <v>5</v>
       </c>
-      <c r="P288">
+      <c r="P288" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q288">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>288</v>
       </c>
-      <c r="Q288" cm="1">
-        <f t="array" ref="Q288">_xlfn.XLOOKUP(
+      <c r="R288" cm="1">
+        <f t="array" ref="R288">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>288</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>779</v>
       </c>
@@ -18268,17 +19154,20 @@
       <c r="N289" t="s">
         <v>5</v>
       </c>
-      <c r="P289">
+      <c r="P289" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q289">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>289</v>
       </c>
-      <c r="Q289" cm="1">
-        <f t="array" ref="Q289">_xlfn.XLOOKUP(
+      <c r="R289" cm="1">
+        <f t="array" ref="R289">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>289</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>779</v>
       </c>
@@ -18318,17 +19207,20 @@
       <c r="N290" t="s">
         <v>194</v>
       </c>
-      <c r="P290">
+      <c r="P290" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q290">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>290</v>
       </c>
-      <c r="Q290" cm="1">
-        <f t="array" ref="Q290">_xlfn.XLOOKUP(
+      <c r="R290" cm="1">
+        <f t="array" ref="R290">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>290</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>779</v>
       </c>
@@ -18368,17 +19260,20 @@
       <c r="N291" t="s">
         <v>194</v>
       </c>
-      <c r="P291">
+      <c r="P291" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q291">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>291</v>
       </c>
-      <c r="Q291" cm="1">
-        <f t="array" ref="Q291">_xlfn.XLOOKUP(
+      <c r="R291" cm="1">
+        <f t="array" ref="R291">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>291</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>779</v>
       </c>
@@ -18418,17 +19313,20 @@
       <c r="N292" t="s">
         <v>5</v>
       </c>
-      <c r="P292">
+      <c r="P292" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q292">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>292</v>
       </c>
-      <c r="Q292" cm="1">
-        <f t="array" ref="Q292">_xlfn.XLOOKUP(
+      <c r="R292" cm="1">
+        <f t="array" ref="R292">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>292</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>779</v>
       </c>
@@ -18468,17 +19366,20 @@
       <c r="N293" t="s">
         <v>194</v>
       </c>
-      <c r="P293">
+      <c r="P293" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q293">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>293</v>
       </c>
-      <c r="Q293" cm="1">
-        <f t="array" ref="Q293">_xlfn.XLOOKUP(
+      <c r="R293" cm="1">
+        <f t="array" ref="R293">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>293</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>779</v>
       </c>
@@ -18518,17 +19419,20 @@
       <c r="N294" t="s">
         <v>194</v>
       </c>
-      <c r="P294">
+      <c r="P294" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q294">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>294</v>
       </c>
-      <c r="Q294" cm="1">
-        <f t="array" ref="Q294">_xlfn.XLOOKUP(
+      <c r="R294" cm="1">
+        <f t="array" ref="R294">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>294</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>779</v>
       </c>
@@ -18568,17 +19472,20 @@
       <c r="N295" t="s">
         <v>5</v>
       </c>
-      <c r="P295">
+      <c r="P295" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q295">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>295</v>
       </c>
-      <c r="Q295" cm="1">
-        <f t="array" ref="Q295">_xlfn.XLOOKUP(
+      <c r="R295" cm="1">
+        <f t="array" ref="R295">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>295</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>779</v>
       </c>
@@ -18618,17 +19525,20 @@
       <c r="N296" t="s">
         <v>194</v>
       </c>
-      <c r="P296">
+      <c r="P296" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q296">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>296</v>
       </c>
-      <c r="Q296" cm="1">
-        <f t="array" ref="Q296">_xlfn.XLOOKUP(
+      <c r="R296" cm="1">
+        <f t="array" ref="R296">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>296</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>779</v>
       </c>
@@ -18668,17 +19578,20 @@
       <c r="N297" t="s">
         <v>194</v>
       </c>
-      <c r="P297">
+      <c r="P297" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q297">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>297</v>
       </c>
-      <c r="Q297" cm="1">
-        <f t="array" ref="Q297">_xlfn.XLOOKUP(
+      <c r="R297" cm="1">
+        <f t="array" ref="R297">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>297</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>854</v>
       </c>
@@ -18718,17 +19631,20 @@
       <c r="N298" t="s">
         <v>5</v>
       </c>
-      <c r="P298">
+      <c r="P298" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q298">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>298</v>
       </c>
-      <c r="Q298" cm="1">
-        <f t="array" ref="Q298">_xlfn.XLOOKUP(
+      <c r="R298" cm="1">
+        <f t="array" ref="R298">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>298</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>854</v>
       </c>
@@ -18768,17 +19684,20 @@
       <c r="N299" t="s">
         <v>5</v>
       </c>
-      <c r="P299">
+      <c r="P299" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q299">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>299</v>
       </c>
-      <c r="Q299" cm="1">
-        <f t="array" ref="Q299">_xlfn.XLOOKUP(
+      <c r="R299" cm="1">
+        <f t="array" ref="R299">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>299</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>854</v>
       </c>
@@ -18818,17 +19737,20 @@
       <c r="N300" t="s">
         <v>5</v>
       </c>
-      <c r="P300">
+      <c r="P300" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q300">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>300</v>
       </c>
-      <c r="Q300" cm="1">
-        <f t="array" ref="Q300">_xlfn.XLOOKUP(
+      <c r="R300" cm="1">
+        <f t="array" ref="R300">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>854</v>
       </c>
@@ -18868,17 +19790,20 @@
       <c r="N301" t="s">
         <v>5</v>
       </c>
-      <c r="P301">
+      <c r="P301" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q301">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>301</v>
       </c>
-      <c r="Q301" cm="1">
-        <f t="array" ref="Q301">_xlfn.XLOOKUP(
+      <c r="R301" cm="1">
+        <f t="array" ref="R301">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>301</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>15</v>
       </c>
@@ -18918,17 +19843,20 @@
       <c r="N302" t="s">
         <v>21</v>
       </c>
-      <c r="P302">
+      <c r="P302" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q302">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>302</v>
       </c>
-      <c r="Q302" cm="1">
-        <f t="array" ref="Q302">_xlfn.XLOOKUP(
+      <c r="R302" cm="1">
+        <f t="array" ref="R302">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>302</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>15</v>
       </c>
@@ -18968,17 +19896,20 @@
       <c r="N303" t="s">
         <v>21</v>
       </c>
-      <c r="P303">
+      <c r="P303" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q303">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>303</v>
       </c>
-      <c r="Q303" cm="1">
-        <f t="array" ref="Q303">_xlfn.XLOOKUP(
+      <c r="R303" cm="1">
+        <f t="array" ref="R303">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>303</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>15</v>
       </c>
@@ -19018,17 +19949,20 @@
       <c r="N304" t="s">
         <v>21</v>
       </c>
-      <c r="P304">
+      <c r="P304" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q304">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>304</v>
       </c>
-      <c r="Q304" cm="1">
-        <f t="array" ref="Q304">_xlfn.XLOOKUP(
+      <c r="R304" cm="1">
+        <f t="array" ref="R304">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>304</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>15</v>
       </c>
@@ -19068,17 +20002,20 @@
       <c r="N305" t="s">
         <v>21</v>
       </c>
-      <c r="P305">
+      <c r="P305" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q305">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>305</v>
       </c>
-      <c r="Q305" cm="1">
-        <f t="array" ref="Q305">_xlfn.XLOOKUP(
+      <c r="R305" cm="1">
+        <f t="array" ref="R305">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>305</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>15</v>
       </c>
@@ -19118,17 +20055,20 @@
       <c r="N306" t="s">
         <v>21</v>
       </c>
-      <c r="P306">
+      <c r="P306" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q306">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>306</v>
       </c>
-      <c r="Q306" cm="1">
-        <f t="array" ref="Q306">_xlfn.XLOOKUP(
+      <c r="R306" cm="1">
+        <f t="array" ref="R306">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>306</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>15</v>
       </c>
@@ -19168,17 +20108,20 @@
       <c r="N307" t="s">
         <v>21</v>
       </c>
-      <c r="P307">
+      <c r="P307" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q307">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>307</v>
       </c>
-      <c r="Q307" cm="1">
-        <f t="array" ref="Q307">_xlfn.XLOOKUP(
+      <c r="R307" cm="1">
+        <f t="array" ref="R307">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>307</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>15</v>
       </c>
@@ -19218,17 +20161,20 @@
       <c r="N308" t="s">
         <v>21</v>
       </c>
-      <c r="P308">
+      <c r="P308" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q308">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>308</v>
       </c>
-      <c r="Q308" cm="1">
-        <f t="array" ref="Q308">_xlfn.XLOOKUP(
+      <c r="R308" cm="1">
+        <f t="array" ref="R308">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>308</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>15</v>
       </c>
@@ -19268,17 +20214,20 @@
       <c r="N309" t="s">
         <v>21</v>
       </c>
-      <c r="P309">
+      <c r="P309" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q309">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>309</v>
       </c>
-      <c r="Q309" cm="1">
-        <f t="array" ref="Q309">_xlfn.XLOOKUP(
+      <c r="R309" cm="1">
+        <f t="array" ref="R309">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>309</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>15</v>
       </c>
@@ -19318,17 +20267,20 @@
       <c r="N310" t="s">
         <v>21</v>
       </c>
-      <c r="P310">
+      <c r="P310" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q310">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>310</v>
       </c>
-      <c r="Q310" cm="1">
-        <f t="array" ref="Q310">_xlfn.XLOOKUP(
+      <c r="R310" cm="1">
+        <f t="array" ref="R310">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>310</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>15</v>
       </c>
@@ -19368,17 +20320,20 @@
       <c r="N311" t="s">
         <v>21</v>
       </c>
-      <c r="P311">
+      <c r="P311" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q311">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>311</v>
       </c>
-      <c r="Q311" cm="1">
-        <f t="array" ref="Q311">_xlfn.XLOOKUP(
+      <c r="R311" cm="1">
+        <f t="array" ref="R311">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>311</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>15</v>
       </c>
@@ -19418,17 +20373,20 @@
       <c r="N312" t="s">
         <v>21</v>
       </c>
-      <c r="P312">
+      <c r="P312" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q312">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>312</v>
       </c>
-      <c r="Q312" cm="1">
-        <f t="array" ref="Q312">_xlfn.XLOOKUP(
+      <c r="R312" cm="1">
+        <f t="array" ref="R312">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>312</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>15</v>
       </c>
@@ -19468,17 +20426,20 @@
       <c r="N313" t="s">
         <v>21</v>
       </c>
-      <c r="P313">
+      <c r="P313" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q313">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>313</v>
       </c>
-      <c r="Q313" cm="1">
-        <f t="array" ref="Q313">_xlfn.XLOOKUP(
+      <c r="R313" cm="1">
+        <f t="array" ref="R313">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>313</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>15</v>
       </c>
@@ -19518,17 +20479,20 @@
       <c r="N314" t="s">
         <v>21</v>
       </c>
-      <c r="P314">
+      <c r="P314" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q314">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>314</v>
       </c>
-      <c r="Q314" cm="1">
-        <f t="array" ref="Q314">_xlfn.XLOOKUP(
+      <c r="R314" cm="1">
+        <f t="array" ref="R314">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>314</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>15</v>
       </c>
@@ -19568,17 +20532,20 @@
       <c r="N315" t="s">
         <v>21</v>
       </c>
-      <c r="P315">
+      <c r="P315" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q315">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>315</v>
       </c>
-      <c r="Q315" cm="1">
-        <f t="array" ref="Q315">_xlfn.XLOOKUP(
+      <c r="R315" cm="1">
+        <f t="array" ref="R315">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>315</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>15</v>
       </c>
@@ -19618,17 +20585,20 @@
       <c r="N316" t="s">
         <v>21</v>
       </c>
-      <c r="P316">
+      <c r="P316" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q316">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>316</v>
       </c>
-      <c r="Q316" cm="1">
-        <f t="array" ref="Q316">_xlfn.XLOOKUP(
+      <c r="R316" cm="1">
+        <f t="array" ref="R316">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>316</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>15</v>
       </c>
@@ -19668,17 +20638,20 @@
       <c r="N317" t="s">
         <v>21</v>
       </c>
-      <c r="P317">
+      <c r="P317" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q317">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>317</v>
       </c>
-      <c r="Q317" cm="1">
-        <f t="array" ref="Q317">_xlfn.XLOOKUP(
+      <c r="R317" cm="1">
+        <f t="array" ref="R317">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>317</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>15</v>
       </c>
@@ -19718,17 +20691,20 @@
       <c r="N318" t="s">
         <v>21</v>
       </c>
-      <c r="P318">
+      <c r="P318" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q318">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>318</v>
       </c>
-      <c r="Q318" cm="1">
-        <f t="array" ref="Q318">_xlfn.XLOOKUP(
+      <c r="R318" cm="1">
+        <f t="array" ref="R318">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>318</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>15</v>
       </c>
@@ -19768,17 +20744,20 @@
       <c r="N319" t="s">
         <v>21</v>
       </c>
-      <c r="P319">
+      <c r="P319" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q319">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>319</v>
       </c>
-      <c r="Q319" cm="1">
-        <f t="array" ref="Q319">_xlfn.XLOOKUP(
+      <c r="R319" cm="1">
+        <f t="array" ref="R319">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>319</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>15</v>
       </c>
@@ -19818,17 +20797,20 @@
       <c r="N320" t="s">
         <v>21</v>
       </c>
-      <c r="P320">
+      <c r="P320" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q320">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>320</v>
       </c>
-      <c r="Q320" cm="1">
-        <f t="array" ref="Q320">_xlfn.XLOOKUP(
+      <c r="R320" cm="1">
+        <f t="array" ref="R320">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>320</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>15</v>
       </c>
@@ -19868,17 +20850,20 @@
       <c r="N321" t="s">
         <v>21</v>
       </c>
-      <c r="P321">
+      <c r="P321" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q321">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>321</v>
       </c>
-      <c r="Q321" cm="1">
-        <f t="array" ref="Q321">_xlfn.XLOOKUP(
+      <c r="R321" cm="1">
+        <f t="array" ref="R321">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>321</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>15</v>
       </c>
@@ -19918,17 +20903,20 @@
       <c r="N322" t="s">
         <v>21</v>
       </c>
-      <c r="P322">
+      <c r="P322" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q322">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>322</v>
       </c>
-      <c r="Q322" cm="1">
-        <f t="array" ref="Q322">_xlfn.XLOOKUP(
+      <c r="R322" cm="1">
+        <f t="array" ref="R322">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>322</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>15</v>
       </c>
@@ -19968,17 +20956,20 @@
       <c r="N323" t="s">
         <v>21</v>
       </c>
-      <c r="P323">
+      <c r="P323" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q323">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>323</v>
       </c>
-      <c r="Q323" cm="1">
-        <f t="array" ref="Q323">_xlfn.XLOOKUP(
+      <c r="R323" cm="1">
+        <f t="array" ref="R323">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>323</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>15</v>
       </c>
@@ -20018,17 +21009,20 @@
       <c r="N324" t="s">
         <v>21</v>
       </c>
-      <c r="P324">
+      <c r="P324" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q324">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>324</v>
       </c>
-      <c r="Q324" cm="1">
-        <f t="array" ref="Q324">_xlfn.XLOOKUP(
+      <c r="R324" cm="1">
+        <f t="array" ref="R324">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>324</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>15</v>
       </c>
@@ -20068,17 +21062,20 @@
       <c r="N325" t="s">
         <v>21</v>
       </c>
-      <c r="P325">
+      <c r="P325" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q325">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>325</v>
       </c>
-      <c r="Q325" cm="1">
-        <f t="array" ref="Q325">_xlfn.XLOOKUP(
+      <c r="R325" cm="1">
+        <f t="array" ref="R325">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>325</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>15</v>
       </c>
@@ -20118,17 +21115,20 @@
       <c r="N326" t="s">
         <v>21</v>
       </c>
-      <c r="P326">
+      <c r="P326" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q326">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>326</v>
       </c>
-      <c r="Q326" cm="1">
-        <f t="array" ref="Q326">_xlfn.XLOOKUP(
+      <c r="R326" cm="1">
+        <f t="array" ref="R326">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>326</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>863</v>
       </c>
@@ -20168,17 +21168,20 @@
       <c r="N327" t="s">
         <v>5</v>
       </c>
-      <c r="P327">
+      <c r="P327" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q327">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>327</v>
       </c>
-      <c r="Q327" cm="1">
-        <f t="array" ref="Q327">_xlfn.XLOOKUP(
+      <c r="R327" cm="1">
+        <f t="array" ref="R327">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>327</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>863</v>
       </c>
@@ -20218,17 +21221,20 @@
       <c r="N328" t="s">
         <v>5</v>
       </c>
-      <c r="P328">
+      <c r="P328" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q328">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>328</v>
       </c>
-      <c r="Q328" cm="1">
-        <f t="array" ref="Q328">_xlfn.XLOOKUP(
+      <c r="R328" cm="1">
+        <f t="array" ref="R328">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>328</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>863</v>
       </c>
@@ -20268,17 +21274,20 @@
       <c r="N329" t="s">
         <v>5</v>
       </c>
-      <c r="P329">
+      <c r="P329" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q329">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>329</v>
       </c>
-      <c r="Q329" cm="1">
-        <f t="array" ref="Q329">_xlfn.XLOOKUP(
+      <c r="R329" cm="1">
+        <f t="array" ref="R329">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>329</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>863</v>
       </c>
@@ -20318,17 +21327,20 @@
       <c r="N330" t="s">
         <v>5</v>
       </c>
-      <c r="P330">
+      <c r="P330" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q330">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>330</v>
       </c>
-      <c r="Q330" cm="1">
-        <f t="array" ref="Q330">_xlfn.XLOOKUP(
+      <c r="R330" cm="1">
+        <f t="array" ref="R330">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>330</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>863</v>
       </c>
@@ -20368,17 +21380,20 @@
       <c r="N331" t="s">
         <v>5</v>
       </c>
-      <c r="P331">
+      <c r="P331" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q331">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>331</v>
       </c>
-      <c r="Q331" cm="1">
-        <f t="array" ref="Q331">_xlfn.XLOOKUP(
+      <c r="R331" cm="1">
+        <f t="array" ref="R331">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>331</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>863</v>
       </c>
@@ -20418,17 +21433,20 @@
       <c r="N332" t="s">
         <v>5</v>
       </c>
-      <c r="P332">
+      <c r="P332" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q332">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>332</v>
       </c>
-      <c r="Q332" cm="1">
-        <f t="array" ref="Q332">_xlfn.XLOOKUP(
+      <c r="R332" cm="1">
+        <f t="array" ref="R332">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>332</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>863</v>
       </c>
@@ -20468,17 +21486,20 @@
       <c r="N333" t="s">
         <v>5</v>
       </c>
-      <c r="P333">
+      <c r="P333" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q333">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>333</v>
       </c>
-      <c r="Q333" cm="1">
-        <f t="array" ref="Q333">_xlfn.XLOOKUP(
+      <c r="R333" cm="1">
+        <f t="array" ref="R333">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>333</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>863</v>
       </c>
@@ -20518,17 +21539,20 @@
       <c r="N334" t="s">
         <v>5</v>
       </c>
-      <c r="P334">
+      <c r="P334" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q334">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>334</v>
       </c>
-      <c r="Q334" cm="1">
-        <f t="array" ref="Q334">_xlfn.XLOOKUP(
+      <c r="R334" cm="1">
+        <f t="array" ref="R334">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>334</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>863</v>
       </c>
@@ -20568,17 +21592,20 @@
       <c r="N335" t="s">
         <v>5</v>
       </c>
-      <c r="P335">
+      <c r="P335" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q335">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>335</v>
       </c>
-      <c r="Q335" cm="1">
-        <f t="array" ref="Q335">_xlfn.XLOOKUP(
+      <c r="R335" cm="1">
+        <f t="array" ref="R335">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>335</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>863</v>
       </c>
@@ -20618,17 +21645,20 @@
       <c r="N336" t="s">
         <v>5</v>
       </c>
-      <c r="P336">
+      <c r="P336" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q336">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>336</v>
       </c>
-      <c r="Q336" cm="1">
-        <f t="array" ref="Q336">_xlfn.XLOOKUP(
+      <c r="R336" cm="1">
+        <f t="array" ref="R336">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>336</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>863</v>
       </c>
@@ -20668,17 +21698,20 @@
       <c r="N337" t="s">
         <v>5</v>
       </c>
-      <c r="P337">
+      <c r="P337" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q337">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>337</v>
       </c>
-      <c r="Q337" cm="1">
-        <f t="array" ref="Q337">_xlfn.XLOOKUP(
+      <c r="R337" cm="1">
+        <f t="array" ref="R337">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>337</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>863</v>
       </c>
@@ -20718,17 +21751,20 @@
       <c r="N338" t="s">
         <v>5</v>
       </c>
-      <c r="P338">
+      <c r="P338" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q338">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>338</v>
       </c>
-      <c r="Q338" cm="1">
-        <f t="array" ref="Q338">_xlfn.XLOOKUP(
+      <c r="R338" cm="1">
+        <f t="array" ref="R338">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>338</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>863</v>
       </c>
@@ -20768,17 +21804,20 @@
       <c r="N339" t="s">
         <v>5</v>
       </c>
-      <c r="P339">
+      <c r="P339" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q339">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>339</v>
       </c>
-      <c r="Q339" cm="1">
-        <f t="array" ref="Q339">_xlfn.XLOOKUP(
+      <c r="R339" cm="1">
+        <f t="array" ref="R339">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>339</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>863</v>
       </c>
@@ -20818,17 +21857,20 @@
       <c r="N340" t="s">
         <v>5</v>
       </c>
-      <c r="P340">
+      <c r="P340" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q340">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>340</v>
       </c>
-      <c r="Q340" cm="1">
-        <f t="array" ref="Q340">_xlfn.XLOOKUP(
+      <c r="R340" cm="1">
+        <f t="array" ref="R340">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>340</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>863</v>
       </c>
@@ -20868,17 +21910,20 @@
       <c r="N341" t="s">
         <v>5</v>
       </c>
-      <c r="P341">
+      <c r="P341" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q341">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>341</v>
       </c>
-      <c r="Q341" cm="1">
-        <f t="array" ref="Q341">_xlfn.XLOOKUP(
+      <c r="R341" cm="1">
+        <f t="array" ref="R341">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>341</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>863</v>
       </c>
@@ -20918,17 +21963,20 @@
       <c r="N342" t="s">
         <v>5</v>
       </c>
-      <c r="P342">
+      <c r="P342" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q342">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>342</v>
       </c>
-      <c r="Q342" cm="1">
-        <f t="array" ref="Q342">_xlfn.XLOOKUP(
+      <c r="R342" cm="1">
+        <f t="array" ref="R342">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>342</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>863</v>
       </c>
@@ -20968,17 +22016,20 @@
       <c r="N343" t="s">
         <v>5</v>
       </c>
-      <c r="P343">
+      <c r="P343" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q343">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>343</v>
       </c>
-      <c r="Q343" cm="1">
-        <f t="array" ref="Q343">_xlfn.XLOOKUP(
+      <c r="R343" cm="1">
+        <f t="array" ref="R343">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>343</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>863</v>
       </c>
@@ -21018,17 +22069,20 @@
       <c r="N344" t="s">
         <v>5</v>
       </c>
-      <c r="P344">
+      <c r="P344" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q344">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>344</v>
       </c>
-      <c r="Q344" cm="1">
-        <f t="array" ref="Q344">_xlfn.XLOOKUP(
+      <c r="R344" cm="1">
+        <f t="array" ref="R344">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>344</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>863</v>
       </c>
@@ -21068,17 +22122,20 @@
       <c r="N345" t="s">
         <v>5</v>
       </c>
-      <c r="P345">
+      <c r="P345" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q345">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>345</v>
       </c>
-      <c r="Q345" cm="1">
-        <f t="array" ref="Q345">_xlfn.XLOOKUP(
+      <c r="R345" cm="1">
+        <f t="array" ref="R345">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>345</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>863</v>
       </c>
@@ -21118,17 +22175,20 @@
       <c r="N346" t="s">
         <v>5</v>
       </c>
-      <c r="P346">
+      <c r="P346" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q346">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>346</v>
       </c>
-      <c r="Q346" cm="1">
-        <f t="array" ref="Q346">_xlfn.XLOOKUP(
+      <c r="R346" cm="1">
+        <f t="array" ref="R346">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>346</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>863</v>
       </c>
@@ -21168,17 +22228,20 @@
       <c r="N347" t="s">
         <v>5</v>
       </c>
-      <c r="P347">
+      <c r="P347" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q347">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>347</v>
       </c>
-      <c r="Q347" cm="1">
-        <f t="array" ref="Q347">_xlfn.XLOOKUP(
+      <c r="R347" cm="1">
+        <f t="array" ref="R347">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>347</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>863</v>
       </c>
@@ -21218,17 +22281,20 @@
       <c r="N348" t="s">
         <v>5</v>
       </c>
-      <c r="P348">
+      <c r="P348" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q348">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>348</v>
       </c>
-      <c r="Q348" cm="1">
-        <f t="array" ref="Q348">_xlfn.XLOOKUP(
+      <c r="R348" cm="1">
+        <f t="array" ref="R348">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>348</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>863</v>
       </c>
@@ -21268,17 +22334,20 @@
       <c r="N349" t="s">
         <v>5</v>
       </c>
-      <c r="P349">
+      <c r="P349" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q349">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>349</v>
       </c>
-      <c r="Q349" cm="1">
-        <f t="array" ref="Q349">_xlfn.XLOOKUP(
+      <c r="R349" cm="1">
+        <f t="array" ref="R349">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>349</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>863</v>
       </c>
@@ -21318,17 +22387,20 @@
       <c r="N350" t="s">
         <v>5</v>
       </c>
-      <c r="P350">
+      <c r="P350" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q350">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>350</v>
       </c>
-      <c r="Q350" cm="1">
-        <f t="array" ref="Q350">_xlfn.XLOOKUP(
+      <c r="R350" cm="1">
+        <f t="array" ref="R350">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>350</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>863</v>
       </c>
@@ -21368,17 +22440,20 @@
       <c r="N351" t="s">
         <v>5</v>
       </c>
-      <c r="P351">
+      <c r="P351" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q351">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>351</v>
       </c>
-      <c r="Q351" cm="1">
-        <f t="array" ref="Q351">_xlfn.XLOOKUP(
+      <c r="R351" cm="1">
+        <f t="array" ref="R351">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>351</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>863</v>
       </c>
@@ -21418,17 +22493,20 @@
       <c r="N352" t="s">
         <v>5</v>
       </c>
-      <c r="P352">
+      <c r="P352" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q352">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>352</v>
       </c>
-      <c r="Q352" cm="1">
-        <f t="array" ref="Q352">_xlfn.XLOOKUP(
+      <c r="R352" cm="1">
+        <f t="array" ref="R352">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>352</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>863</v>
       </c>
@@ -21468,17 +22546,20 @@
       <c r="N353" t="s">
         <v>5</v>
       </c>
-      <c r="P353">
+      <c r="P353" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q353">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>353</v>
       </c>
-      <c r="Q353" cm="1">
-        <f t="array" ref="Q353">_xlfn.XLOOKUP(
+      <c r="R353" cm="1">
+        <f t="array" ref="R353">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>353</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>863</v>
       </c>
@@ -21518,17 +22599,20 @@
       <c r="N354" t="s">
         <v>5</v>
       </c>
-      <c r="P354">
+      <c r="P354" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q354">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>354</v>
       </c>
-      <c r="Q354" cm="1">
-        <f t="array" ref="Q354">_xlfn.XLOOKUP(
+      <c r="R354" cm="1">
+        <f t="array" ref="R354">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>354</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>863</v>
       </c>
@@ -21568,17 +22652,20 @@
       <c r="N355" t="s">
         <v>5</v>
       </c>
-      <c r="P355">
+      <c r="P355" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q355">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>355</v>
       </c>
-      <c r="Q355" cm="1">
-        <f t="array" ref="Q355">_xlfn.XLOOKUP(
+      <c r="R355" cm="1">
+        <f t="array" ref="R355">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>355</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>863</v>
       </c>
@@ -21618,17 +22705,20 @@
       <c r="N356" t="s">
         <v>5</v>
       </c>
-      <c r="P356">
+      <c r="P356" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q356">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>356</v>
       </c>
-      <c r="Q356" cm="1">
-        <f t="array" ref="Q356">_xlfn.XLOOKUP(
+      <c r="R356" cm="1">
+        <f t="array" ref="R356">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>356</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>863</v>
       </c>
@@ -21668,17 +22758,20 @@
       <c r="N357" t="s">
         <v>5</v>
       </c>
-      <c r="P357">
+      <c r="P357" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q357">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>357</v>
       </c>
-      <c r="Q357" cm="1">
-        <f t="array" ref="Q357">_xlfn.XLOOKUP(
+      <c r="R357" cm="1">
+        <f t="array" ref="R357">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>357</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>863</v>
       </c>
@@ -21718,17 +22811,20 @@
       <c r="N358" t="s">
         <v>5</v>
       </c>
-      <c r="P358">
+      <c r="P358" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q358">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>358</v>
       </c>
-      <c r="Q358" cm="1">
-        <f t="array" ref="Q358">_xlfn.XLOOKUP(
+      <c r="R358" cm="1">
+        <f t="array" ref="R358">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>358</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>863</v>
       </c>
@@ -21768,17 +22864,20 @@
       <c r="N359" t="s">
         <v>5</v>
       </c>
-      <c r="P359">
+      <c r="P359" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q359">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>359</v>
       </c>
-      <c r="Q359" cm="1">
-        <f t="array" ref="Q359">_xlfn.XLOOKUP(
+      <c r="R359" cm="1">
+        <f t="array" ref="R359">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>359</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>863</v>
       </c>
@@ -21818,17 +22917,20 @@
       <c r="N360" t="s">
         <v>5</v>
       </c>
-      <c r="P360">
+      <c r="P360" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q360">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>360</v>
       </c>
-      <c r="Q360" cm="1">
-        <f t="array" ref="Q360">_xlfn.XLOOKUP(
+      <c r="R360" cm="1">
+        <f t="array" ref="R360">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>360</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>863</v>
       </c>
@@ -21868,17 +22970,20 @@
       <c r="N361" t="s">
         <v>5</v>
       </c>
-      <c r="P361">
+      <c r="P361" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q361">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>361</v>
       </c>
-      <c r="Q361" cm="1">
-        <f t="array" ref="Q361">_xlfn.XLOOKUP(
+      <c r="R361" cm="1">
+        <f t="array" ref="R361">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>361</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>915</v>
       </c>
@@ -21918,17 +23023,20 @@
       <c r="N362" t="s">
         <v>5</v>
       </c>
-      <c r="P362">
+      <c r="P362" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q362">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>362</v>
       </c>
-      <c r="Q362" cm="1">
-        <f t="array" ref="Q362">_xlfn.XLOOKUP(
+      <c r="R362" cm="1">
+        <f t="array" ref="R362">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>362</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>915</v>
       </c>
@@ -21968,17 +23076,20 @@
       <c r="N363" t="s">
         <v>5</v>
       </c>
-      <c r="P363">
+      <c r="P363" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q363">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>363</v>
       </c>
-      <c r="Q363" cm="1">
-        <f t="array" ref="Q363">_xlfn.XLOOKUP(
+      <c r="R363" cm="1">
+        <f t="array" ref="R363">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>363</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>918</v>
       </c>
@@ -22018,17 +23129,20 @@
       <c r="N364" t="s">
         <v>5</v>
       </c>
-      <c r="P364">
+      <c r="P364" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q364">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>364</v>
       </c>
-      <c r="Q364" cm="1">
-        <f t="array" ref="Q364">_xlfn.XLOOKUP(
+      <c r="R364" cm="1">
+        <f t="array" ref="R364">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>918</v>
       </c>
@@ -22068,17 +23182,20 @@
       <c r="N365" t="s">
         <v>5</v>
       </c>
-      <c r="P365">
+      <c r="P365" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q365">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>365</v>
       </c>
-      <c r="Q365" cm="1">
-        <f t="array" ref="Q365">_xlfn.XLOOKUP(
+      <c r="R365" cm="1">
+        <f t="array" ref="R365">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>918</v>
       </c>
@@ -22118,17 +23235,20 @@
       <c r="N366" t="s">
         <v>5</v>
       </c>
-      <c r="P366">
+      <c r="P366" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q366">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>366</v>
       </c>
-      <c r="Q366" cm="1">
-        <f t="array" ref="Q366">_xlfn.XLOOKUP(
+      <c r="R366" cm="1">
+        <f t="array" ref="R366">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>918</v>
       </c>
@@ -22168,17 +23288,20 @@
       <c r="N367" t="s">
         <v>5</v>
       </c>
-      <c r="P367">
+      <c r="P367" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q367">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>367</v>
       </c>
-      <c r="Q367" cm="1">
-        <f t="array" ref="Q367">_xlfn.XLOOKUP(
+      <c r="R367" cm="1">
+        <f t="array" ref="R367">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>918</v>
       </c>
@@ -22218,17 +23341,20 @@
       <c r="N368" t="s">
         <v>5</v>
       </c>
-      <c r="P368">
+      <c r="P368" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q368">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>368</v>
       </c>
-      <c r="Q368" cm="1">
-        <f t="array" ref="Q368">_xlfn.XLOOKUP(
+      <c r="R368" cm="1">
+        <f t="array" ref="R368">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>918</v>
       </c>
@@ -22268,17 +23394,20 @@
       <c r="N369" t="s">
         <v>5</v>
       </c>
-      <c r="P369">
+      <c r="P369" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q369">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>369</v>
       </c>
-      <c r="Q369" cm="1">
-        <f t="array" ref="Q369">_xlfn.XLOOKUP(
+      <c r="R369" cm="1">
+        <f t="array" ref="R369">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>918</v>
       </c>
@@ -22318,17 +23447,20 @@
       <c r="N370" t="s">
         <v>5</v>
       </c>
-      <c r="P370">
+      <c r="P370" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q370">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>370</v>
       </c>
-      <c r="Q370" cm="1">
-        <f t="array" ref="Q370">_xlfn.XLOOKUP(
+      <c r="R370" cm="1">
+        <f t="array" ref="R370">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>918</v>
       </c>
@@ -22368,17 +23500,20 @@
       <c r="N371" t="s">
         <v>5</v>
       </c>
-      <c r="P371">
+      <c r="P371" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q371">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>371</v>
       </c>
-      <c r="Q371" cm="1">
-        <f t="array" ref="Q371">_xlfn.XLOOKUP(
+      <c r="R371" cm="1">
+        <f t="array" ref="R371">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>918</v>
       </c>
@@ -22418,17 +23553,20 @@
       <c r="N372" t="s">
         <v>5</v>
       </c>
-      <c r="P372">
+      <c r="P372" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q372">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>372</v>
       </c>
-      <c r="Q372" cm="1">
-        <f t="array" ref="Q372">_xlfn.XLOOKUP(
+      <c r="R372" cm="1">
+        <f t="array" ref="R372">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>918</v>
       </c>
@@ -22468,17 +23606,20 @@
       <c r="N373" t="s">
         <v>5</v>
       </c>
-      <c r="P373">
+      <c r="P373" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q373">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>373</v>
       </c>
-      <c r="Q373" cm="1">
-        <f t="array" ref="Q373">_xlfn.XLOOKUP(
+      <c r="R373" cm="1">
+        <f t="array" ref="R373">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>918</v>
       </c>
@@ -22518,17 +23659,20 @@
       <c r="N374" t="s">
         <v>5</v>
       </c>
-      <c r="P374">
+      <c r="P374" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q374">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>374</v>
       </c>
-      <c r="Q374" cm="1">
-        <f t="array" ref="Q374">_xlfn.XLOOKUP(
+      <c r="R374" cm="1">
+        <f t="array" ref="R374">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>918</v>
       </c>
@@ -22568,17 +23712,20 @@
       <c r="N375" t="s">
         <v>5</v>
       </c>
-      <c r="P375">
+      <c r="P375" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q375">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>375</v>
       </c>
-      <c r="Q375" cm="1">
-        <f t="array" ref="Q375">_xlfn.XLOOKUP(
+      <c r="R375" cm="1">
+        <f t="array" ref="R375">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>918</v>
       </c>
@@ -22618,17 +23765,20 @@
       <c r="N376" t="s">
         <v>5</v>
       </c>
-      <c r="P376">
+      <c r="P376" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q376">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>376</v>
       </c>
-      <c r="Q376" cm="1">
-        <f t="array" ref="Q376">_xlfn.XLOOKUP(
+      <c r="R376" cm="1">
+        <f t="array" ref="R376">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>918</v>
       </c>
@@ -22668,17 +23818,20 @@
       <c r="N377" t="s">
         <v>5</v>
       </c>
-      <c r="P377">
+      <c r="P377" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q377">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>377</v>
       </c>
-      <c r="Q377" cm="1">
-        <f t="array" ref="Q377">_xlfn.XLOOKUP(
+      <c r="R377" cm="1">
+        <f t="array" ref="R377">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>918</v>
       </c>
@@ -22718,17 +23871,20 @@
       <c r="N378" t="s">
         <v>5</v>
       </c>
-      <c r="P378">
+      <c r="P378" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q378">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>378</v>
       </c>
-      <c r="Q378" cm="1">
-        <f t="array" ref="Q378">_xlfn.XLOOKUP(
+      <c r="R378" cm="1">
+        <f t="array" ref="R378">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>918</v>
       </c>
@@ -22768,17 +23924,20 @@
       <c r="N379" t="s">
         <v>5</v>
       </c>
-      <c r="P379">
+      <c r="P379" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q379">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>379</v>
       </c>
-      <c r="Q379" cm="1">
-        <f t="array" ref="Q379">_xlfn.XLOOKUP(
+      <c r="R379" cm="1">
+        <f t="array" ref="R379">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>918</v>
       </c>
@@ -22818,17 +23977,20 @@
       <c r="N380" t="s">
         <v>5</v>
       </c>
-      <c r="P380">
+      <c r="P380" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q380">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>380</v>
       </c>
-      <c r="Q380" cm="1">
-        <f t="array" ref="Q380">_xlfn.XLOOKUP(
+      <c r="R380" cm="1">
+        <f t="array" ref="R380">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>918</v>
       </c>
@@ -22868,17 +24030,20 @@
       <c r="N381" t="s">
         <v>5</v>
       </c>
-      <c r="P381">
+      <c r="P381" t="s">
+        <v>948</v>
+      </c>
+      <c r="Q381">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>381</v>
       </c>
-      <c r="Q381" cm="1">
-        <f t="array" ref="Q381">_xlfn.XLOOKUP(
+      <c r="R381" cm="1">
+        <f t="array" ref="R381">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>381</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>2</v>
       </c>
@@ -22918,17 +24083,20 @@
       <c r="N382" t="s">
         <v>5</v>
       </c>
-      <c r="P382">
+      <c r="P382" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q382">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>382</v>
       </c>
-      <c r="Q382" cm="1">
-        <f t="array" ref="Q382">_xlfn.XLOOKUP(
+      <c r="R382" cm="1">
+        <f t="array" ref="R382">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>2</v>
       </c>
@@ -22968,17 +24136,20 @@
       <c r="N383" t="s">
         <v>5</v>
       </c>
-      <c r="P383">
+      <c r="P383" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q383">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>383</v>
       </c>
-      <c r="Q383" cm="1">
-        <f t="array" ref="Q383">_xlfn.XLOOKUP(
+      <c r="R383" cm="1">
+        <f t="array" ref="R383">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>2</v>
       </c>
@@ -23018,17 +24189,20 @@
       <c r="N384" t="s">
         <v>5</v>
       </c>
-      <c r="P384">
+      <c r="P384" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q384">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>384</v>
       </c>
-      <c r="Q384" cm="1">
-        <f t="array" ref="Q384">_xlfn.XLOOKUP(
+      <c r="R384" cm="1">
+        <f t="array" ref="R384">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>2</v>
       </c>
@@ -23068,17 +24242,20 @@
       <c r="N385" t="s">
         <v>5</v>
       </c>
-      <c r="P385">
+      <c r="P385" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q385">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>385</v>
       </c>
-      <c r="Q385" cm="1">
-        <f t="array" ref="Q385">_xlfn.XLOOKUP(
+      <c r="R385" cm="1">
+        <f t="array" ref="R385">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>2</v>
       </c>
@@ -23118,17 +24295,20 @@
       <c r="N386" t="s">
         <v>5</v>
       </c>
-      <c r="P386">
+      <c r="P386" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q386">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>386</v>
       </c>
-      <c r="Q386" cm="1">
-        <f t="array" ref="Q386">_xlfn.XLOOKUP(
+      <c r="R386" cm="1">
+        <f t="array" ref="R386">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>2</v>
       </c>
@@ -23168,17 +24348,20 @@
       <c r="N387" t="s">
         <v>5</v>
       </c>
-      <c r="P387">
+      <c r="P387" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q387">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>387</v>
       </c>
-      <c r="Q387" cm="1">
-        <f t="array" ref="Q387">_xlfn.XLOOKUP(
+      <c r="R387" cm="1">
+        <f t="array" ref="R387">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>2</v>
       </c>
@@ -23218,17 +24401,20 @@
       <c r="N388" t="s">
         <v>5</v>
       </c>
-      <c r="P388">
+      <c r="P388" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q388">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>388</v>
       </c>
-      <c r="Q388" cm="1">
-        <f t="array" ref="Q388">_xlfn.XLOOKUP(
+      <c r="R388" cm="1">
+        <f t="array" ref="R388">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>2</v>
       </c>
@@ -23268,17 +24454,20 @@
       <c r="N389" t="s">
         <v>5</v>
       </c>
-      <c r="P389">
+      <c r="P389" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q389">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>389</v>
       </c>
-      <c r="Q389" cm="1">
-        <f t="array" ref="Q389">_xlfn.XLOOKUP(
+      <c r="R389" cm="1">
+        <f t="array" ref="R389">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>389</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>937</v>
       </c>
@@ -23318,17 +24507,17 @@
       <c r="N390" t="s">
         <v>5</v>
       </c>
-      <c r="P390">
+      <c r="Q390">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>390</v>
       </c>
-      <c r="Q390" cm="1">
-        <f t="array" ref="Q390">_xlfn.XLOOKUP(
+      <c r="R390" cm="1">
+        <f t="array" ref="R390">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>390</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>939</v>
       </c>
@@ -23368,17 +24557,20 @@
       <c r="N391" t="s">
         <v>5</v>
       </c>
-      <c r="P391">
+      <c r="P391" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q391">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>391</v>
       </c>
-      <c r="Q391" cm="1">
-        <f t="array" ref="Q391">_xlfn.XLOOKUP(
+      <c r="R391" cm="1">
+        <f t="array" ref="R391">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>391</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>939</v>
       </c>
@@ -23418,17 +24610,20 @@
       <c r="N392" t="s">
         <v>5</v>
       </c>
-      <c r="P392">
+      <c r="P392" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q392">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>392</v>
       </c>
-      <c r="Q392" cm="1">
-        <f t="array" ref="Q392">_xlfn.XLOOKUP(
+      <c r="R392" cm="1">
+        <f t="array" ref="R392">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>392</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>939</v>
       </c>
@@ -23468,17 +24663,20 @@
       <c r="N393" t="s">
         <v>5</v>
       </c>
-      <c r="P393">
+      <c r="P393" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q393">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>393</v>
       </c>
-      <c r="Q393" cm="1">
-        <f t="array" ref="Q393">_xlfn.XLOOKUP(
+      <c r="R393" cm="1">
+        <f t="array" ref="R393">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>393</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>939</v>
       </c>
@@ -23518,12 +24716,15 @@
       <c r="N394" t="s">
         <v>5</v>
       </c>
-      <c r="P394">
+      <c r="P394" t="s">
+        <v>946</v>
+      </c>
+      <c r="Q394">
         <f>ROW(Guide[[#This Row],[Row]])</f>
         <v>394</v>
       </c>
-      <c r="Q394" cm="1">
-        <f t="array" ref="Q394">_xlfn.XLOOKUP(
+      <c r="R394" cm="1">
+        <f t="array" ref="R394">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</f>
         <v>394</v>
       </c>

--- a/app/data/Reference/guide.xlsx
+++ b/app/data/Reference/guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csvnewzealand-my.sharepoint.com/personal/mike_csv_co_nz/Documents/06_Altitude/Altitude/app/data/Reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="8_{BCBC3A3A-E0FA-4AA3-8593-2140AD00DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{293F27D8-757B-47A2-88BF-67F36C935195}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="8_{BCBC3A3A-E0FA-4AA3-8593-2140AD00DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C4EA9B3-732C-4CBB-9908-FFBF1D8EC9BE}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="-21600" windowWidth="19380" windowHeight="20970" xr2:uid="{8E4D9682-10B3-4A32-8A23-CE2B94AA5C11}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" xr2:uid="{8E4D9682-10B3-4A32-8A23-CE2B94AA5C11}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5116" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5116" uniqueCount="950">
   <si>
     <t>Tick</t>
   </si>
@@ -2903,6 +2903,9 @@
   </si>
   <si>
     <t>Bar</t>
+  </si>
+  <si>
+    <t>Net</t>
   </si>
 </sst>
 </file>
@@ -3499,19 +3502,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}" name="Guide" displayName="Guide" ref="A1:R394" totalsRowShown="0">
   <autoFilter ref="A1:R394" xr:uid="{718E32A5-9196-4D58-A924-8B1110BC243E}">
-    <filterColumn colId="15">
+    <filterColumn colId="0">
       <filters>
-        <filter val="NA"/>
+        <filter val="hm4"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O34">
-    <sortCondition ref="A2:A34"/>
-    <sortCondition ref="D2:D34"/>
-    <sortCondition ref="E2:E34"/>
-    <sortCondition ref="F2:F34"/>
-    <sortCondition ref="C2:C34"/>
-  </sortState>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{1E105523-1F9A-490B-B3B3-B8269576F2CA}" name="Dataset"/>
     <tableColumn id="2" xr3:uid="{3395981A-EBAB-4924-9326-47FB19E5DA48}" name="DatasetColumn"/>
@@ -3528,11 +3524,11 @@
     <tableColumn id="8" xr3:uid="{CD0AAC95-D2CD-4D30-9011-9942EBEBB4C1}" name="Dim_Label"/>
     <tableColumn id="9" xr3:uid="{20D4E739-3650-49F4-B4E1-DAD4BEFED02E}" name="Tick"/>
     <tableColumn id="10" xr3:uid="{FF813B21-86DC-48A9-A6EA-F4F229F2A91A}" name="Prefix"/>
-    <tableColumn id="12" xr3:uid="{A960F109-EFC6-45B0-838E-89D0D182C4EE}" name="Style" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{58341DB7-5CB8-472C-8948-416C2373B4BA}" name="Row" dataDxfId="2">
+    <tableColumn id="12" xr3:uid="{A960F109-EFC6-45B0-838E-89D0D182C4EE}" name="Style" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{58341DB7-5CB8-472C-8948-416C2373B4BA}" name="Row" dataDxfId="1">
       <calculatedColumnFormula>ROW(Guide[[#This Row],[Row]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D6E30528-2360-40F7-A607-B78AA4014508}" name="Stack" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{D6E30528-2360-40F7-A607-B78AA4014508}" name="Stack" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(
 Guide[[#This Row],[Dataset]]&amp;Guide[[#This Row],[Category_1]]&amp;Guide[[#This Row],[Category_2]]&amp;Guide[[#This Row],[Dim_Group]],_xlfn.ANCHORARRAY( Sheet1!$N$2),_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(Sheet1!$I$2),5),0)</calculatedColumnFormula>
     </tableColumn>
@@ -3865,7 +3861,8 @@
     <col min="2" max="2" width="24.58203125" customWidth="1"/>
     <col min="3" max="3" width="50.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.08203125" customWidth="1"/>
+    <col min="5" max="5" width="58.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.08203125" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="11" width="15.08203125" customWidth="1"/>
     <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -5949,7 +5946,7 @@
         <v>99</v>
       </c>
       <c r="L40" t="s">
-        <v>224</v>
+        <v>949</v>
       </c>
       <c r="M40" t="s">
         <v>224</v>
@@ -6426,7 +6423,7 @@
         <v>99</v>
       </c>
       <c r="L49" t="s">
-        <v>224</v>
+        <v>949</v>
       </c>
       <c r="M49" t="s">
         <v>224</v>
@@ -6903,7 +6900,7 @@
         <v>99</v>
       </c>
       <c r="L58" t="s">
-        <v>224</v>
+        <v>949</v>
       </c>
       <c r="M58" t="s">
         <v>224</v>
@@ -11164,7 +11161,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>414</v>
       </c>
@@ -11217,7 +11214,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>414</v>
       </c>
@@ -11270,7 +11267,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>414</v>
       </c>
@@ -11323,7 +11320,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>414</v>
       </c>
@@ -11376,7 +11373,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>414</v>
       </c>
@@ -11429,7 +11426,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>414</v>
       </c>
@@ -11482,7 +11479,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>414</v>
       </c>
@@ -11535,7 +11532,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>414</v>
       </c>
@@ -11588,7 +11585,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>414</v>
       </c>
@@ -11641,7 +11638,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>414</v>
       </c>
@@ -11694,7 +11691,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>414</v>
       </c>
@@ -11747,7 +11744,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>414</v>
       </c>
@@ -11800,7 +11797,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>414</v>
       </c>
@@ -11853,7 +11850,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>414</v>
       </c>
@@ -11906,7 +11903,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>414</v>
       </c>
@@ -11959,7 +11956,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>414</v>
       </c>
@@ -12012,7 +12009,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>414</v>
       </c>
@@ -12065,7 +12062,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>414</v>
       </c>
@@ -12118,7 +12115,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>414</v>
       </c>
@@ -12171,7 +12168,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>414</v>
       </c>
@@ -12224,7 +12221,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>414</v>
       </c>
@@ -12277,7 +12274,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>414</v>
       </c>
@@ -24467,7 +24464,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>937</v>
       </c>
@@ -26422,13 +26419,13 @@
         <v>Opening position</v>
       </c>
       <c r="L42" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="M42">
         <v>58</v>
       </c>
       <c r="N42" t="str">
-        <v>hc35&lt;=80% LVROpening positionNZDm</v>
+        <v>hc35&lt;=80% LVROpening positionNet</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -26791,13 +26788,13 @@
         <v>Opening position</v>
       </c>
       <c r="L51" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="M51">
         <v>49</v>
       </c>
       <c r="N51" t="str">
-        <v>hc35&gt;80% LVROpening positionNZDm</v>
+        <v>hc35&gt;80% LVROpening positionNet</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -27160,13 +27157,13 @@
         <v>Opening position</v>
       </c>
       <c r="L60" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="M60">
         <v>40</v>
       </c>
       <c r="N60" t="str">
-        <v>hc35TotalOpening positionNZDm</v>
+        <v>hc35TotalOpening positionNet</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -27637,7 +27634,7 @@
         <v>NZDm</v>
       </c>
       <c r="F72" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="G72">
         <v>58</v>
@@ -28006,7 +28003,7 @@
         <v>NZDm</v>
       </c>
       <c r="F81" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="G81">
         <v>49</v>
@@ -28375,7 +28372,7 @@
         <v>NZDm</v>
       </c>
       <c r="F90" t="str">
-        <v>NZDm</v>
+        <v>Net</v>
       </c>
       <c r="G90">
         <v>40</v>
